--- a/packages/calculators/src/modules/test/14-electricity.xlsx
+++ b/packages/calculators/src/modules/test/14-electricity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators/packages/calculators/src/modules/test/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators-internal/packages/calculators/src/modules/test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F45D962-3960-A544-970D-8F89D1F49E9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20066D07-B7A9-FD4E-8E1A-6773CAF67D66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51220" yWindow="18580" windowWidth="28800" windowHeight="23520" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="15900" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
   </bookViews>
   <sheets>
     <sheet name="14.1.1.1" sheetId="3" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="42">
   <si>
     <t>Method 1</t>
   </si>
@@ -127,42 +127,12 @@
     <t>Scope 2 Emission Factors (kg CO2-e/kWh)</t>
   </si>
   <si>
-    <t>Scope 2 Emission Factors (kg CO2-e/GJ)</t>
-  </si>
-  <si>
     <t>Scope 3 Emission Factors (kg CO2-e/kWh)</t>
   </si>
   <si>
-    <t>Scope 3 Emission Factors (kg CO2-e/GJ)</t>
-  </si>
-  <si>
     <t>National</t>
   </si>
   <si>
-    <t>nsw</t>
-  </si>
-  <si>
-    <t>vic</t>
-  </si>
-  <si>
-    <t>qld</t>
-  </si>
-  <si>
-    <t>sa</t>
-  </si>
-  <si>
-    <t>wa_sw</t>
-  </si>
-  <si>
-    <t>wa_nw</t>
-  </si>
-  <si>
-    <t>tas</t>
-  </si>
-  <si>
-    <t>nt</t>
-  </si>
-  <si>
     <t>EF2elec</t>
   </si>
   <si>
@@ -178,12 +148,6 @@
     <t>JRPP</t>
   </si>
   <si>
-    <t>E2elec mb</t>
-  </si>
-  <si>
-    <t>E2elec lb</t>
-  </si>
-  <si>
     <t>RMF</t>
   </si>
   <si>
@@ -200,9 +164,6 @@
   </si>
   <si>
     <t>NGAF 2023 p10</t>
-  </si>
-  <si>
-    <t>act</t>
   </si>
   <si>
     <t>Non renewables</t>
@@ -345,16 +306,52 @@
     </r>
   </si>
   <si>
-    <t>E3elec lb</t>
-  </si>
-  <si>
-    <t>E3elec mb</t>
-  </si>
-  <si>
     <t>EF3elec</t>
   </si>
   <si>
     <t>EFrmf3elec</t>
+  </si>
+  <si>
+    <t>MWh</t>
+  </si>
+  <si>
+    <t>E2elec (Location)</t>
+  </si>
+  <si>
+    <t>E2elec (Market)</t>
+  </si>
+  <si>
+    <t>E3elec (Location)</t>
+  </si>
+  <si>
+    <t>E3elec (Market)</t>
+  </si>
+  <si>
+    <t>NSW</t>
+  </si>
+  <si>
+    <t>VIC</t>
+  </si>
+  <si>
+    <t>QLD</t>
+  </si>
+  <si>
+    <t>SA</t>
+  </si>
+  <si>
+    <t>WA_SW</t>
+  </si>
+  <si>
+    <t>WA_NW</t>
+  </si>
+  <si>
+    <t>TAS</t>
+  </si>
+  <si>
+    <t>NT</t>
+  </si>
+  <si>
+    <t>ACT</t>
   </si>
 </sst>
 </file>
@@ -398,13 +395,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -421,6 +411,14 @@
       <sz val="12"/>
       <name val="Menlo"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -452,8 +450,9 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -464,11 +463,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -479,20 +477,22 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -855,588 +855,535 @@
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="K1" s="20" t="s">
+      <c r="K1" s="19" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="50" customHeight="1">
-      <c r="L2" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="N2" s="20" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18">
+      <c r="L2" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" s="19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="17">
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
+      <c r="C3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
       <c r="J3" s="1" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="K3" s="1"/>
-      <c r="M3" s="7"/>
+      <c r="M3" s="6"/>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
       <c r="Q3" s="1"/>
     </row>
     <row r="4" spans="1:18" ht="17">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J4" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" t="s">
-        <v>42</v>
-      </c>
-      <c r="I4" t="s">
-        <v>24</v>
-      </c>
-      <c r="J4" t="s">
-        <v>34</v>
-      </c>
       <c r="K4" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="P4" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="Q4">
         <v>0.16669999999999999</v>
       </c>
-      <c r="R4" s="6" t="s">
-        <v>30</v>
+      <c r="R4" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5">
         <v>1000</v>
       </c>
-      <c r="B5" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12">
+      <c r="B5" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11">
         <f t="shared" ref="E5:E13" si="0">IF(ISBLANK(A5), "", VLOOKUP(B5, $P$20:$T$28, 2, FALSE))</f>
-        <v>0.68</v>
-      </c>
-      <c r="F5" s="12">
+        <v>0.66</v>
+      </c>
+      <c r="F5" s="11">
         <f>IF(ISBLANK(A5), "", VLOOKUP(B5, $P$20:$T$28, 4, FALSE))</f>
-        <v>0.05</v>
-      </c>
-      <c r="G5" s="12">
+        <v>0.04</v>
+      </c>
+      <c r="G5" s="11">
         <f>$Q$15</f>
         <v>0.81</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="11">
         <f>$R$15</f>
         <v>0.1</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="11">
         <f t="shared" ref="I5:I13" si="1">IF(ISBLANK(A5), "", IF(B5="act", $Q$5, 0))</f>
         <v>0</v>
       </c>
-      <c r="J5" s="12">
-        <f t="shared" ref="J5:J23" si="2">A5*(1-($Q$4+I5))-((C5-D5)/1000)</f>
+      <c r="J5" s="11">
+        <f>A5*(1-($Q$4+I5))-((C5-D5)*1000)</f>
         <v>833.30000000000007</v>
       </c>
-      <c r="K5" s="12">
-        <f t="shared" ref="K5:K13" si="3">A5*E5/1000</f>
-        <v>0.68</v>
-      </c>
-      <c r="L5" s="12">
-        <f t="shared" ref="L5:L23" si="4">IF(ISBLANK(A5), "", J5*G5/1000)</f>
-        <v>0.67497300000000005</v>
-      </c>
-      <c r="M5" s="12">
+      <c r="K5" s="11">
+        <f>A5*E5/1000</f>
+        <v>0.66</v>
+      </c>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11">
         <f>IF(ISBLANK(A5), "", A5*F5/1000)</f>
-        <v>0.05</v>
-      </c>
-      <c r="N5" s="12">
-        <f>IF(ISBLANK(A5), "", J5*H5/1000)</f>
-        <v>8.3330000000000015E-2</v>
-      </c>
-      <c r="O5" s="12"/>
+        <v>0.04</v>
+      </c>
+      <c r="N5" s="11"/>
+      <c r="O5" s="11"/>
       <c r="P5" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="Q5">
-        <v>0.74129999999999996</v>
+        <v>0.79510000000000003</v>
       </c>
       <c r="R5" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:18">
       <c r="A6">
         <v>2000</v>
       </c>
-      <c r="B6" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12">
+      <c r="B6" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11">
         <f t="shared" si="0"/>
-        <v>0.79</v>
-      </c>
-      <c r="F6" s="12">
-        <f t="shared" ref="F6:F23" si="5">IF(ISBLANK(A6), "", VLOOKUP(B6, $P$20:$T$28, 4, FALSE))</f>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="G6" s="12">
-        <f t="shared" ref="G6:G13" si="6">$Q$15</f>
+        <v>0.77</v>
+      </c>
+      <c r="F6" s="11">
+        <f t="shared" ref="F6:F23" si="2">IF(ISBLANK(A6), "", VLOOKUP(B6, $P$20:$T$28, 4, FALSE))</f>
+        <v>0.09</v>
+      </c>
+      <c r="G6" s="11">
+        <f t="shared" ref="G6:G13" si="3">$Q$15</f>
         <v>0.81</v>
       </c>
-      <c r="H6" s="12">
-        <f t="shared" ref="H6:H23" si="7">$R$15</f>
+      <c r="H6" s="11">
+        <f t="shared" ref="H6:H23" si="4">$R$15</f>
         <v>0.1</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J6" s="12">
-        <f t="shared" si="2"/>
+      <c r="J6" s="11">
+        <f t="shared" ref="J6:J23" si="5">A6*(1-($Q$4+I6))-((C6-D6)*1000)</f>
         <v>1666.6000000000001</v>
       </c>
-      <c r="K6" s="12">
-        <f t="shared" si="3"/>
-        <v>1.58</v>
-      </c>
-      <c r="L6" s="12">
-        <f t="shared" si="4"/>
-        <v>1.3499460000000001</v>
-      </c>
-      <c r="M6" s="12">
-        <f t="shared" ref="M6:M23" si="8">IF(ISBLANK(A6), "", A6*F6/1000)</f>
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="N6" s="12">
-        <f t="shared" ref="N6:N23" si="9">IF(ISBLANK(A6), "", J6*H6/1000)</f>
-        <v>0.16666000000000003</v>
-      </c>
-      <c r="O6" s="12"/>
+      <c r="K6" s="11">
+        <f t="shared" ref="K6:K13" si="6">A6*E6/1000</f>
+        <v>1.54</v>
+      </c>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11">
+        <f t="shared" ref="M6:M14" si="7">IF(ISBLANK(A6), "", A6*F6/1000)</f>
+        <v>0.18</v>
+      </c>
+      <c r="N6" s="11"/>
+      <c r="O6" s="11"/>
     </row>
     <row r="7" spans="1:18">
       <c r="A7">
         <v>3000</v>
       </c>
-      <c r="B7" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12">
+      <c r="B7" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11">
         <f t="shared" si="0"/>
-        <v>0.73</v>
-      </c>
-      <c r="F7" s="12">
-        <f t="shared" si="5"/>
-        <v>0.15</v>
-      </c>
-      <c r="G7" s="12">
-        <f t="shared" si="6"/>
+        <v>0.71</v>
+      </c>
+      <c r="F7" s="11">
+        <f t="shared" si="2"/>
+        <v>0.1</v>
+      </c>
+      <c r="G7" s="11">
+        <f t="shared" si="3"/>
         <v>0.81</v>
       </c>
-      <c r="H7" s="12">
-        <f t="shared" si="7"/>
+      <c r="H7" s="11">
+        <f t="shared" si="4"/>
         <v>0.1</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J7" s="12">
-        <f t="shared" si="2"/>
+      <c r="J7" s="11">
+        <f t="shared" si="5"/>
         <v>2499.9</v>
       </c>
-      <c r="K7" s="12">
-        <f t="shared" si="3"/>
-        <v>2.19</v>
-      </c>
-      <c r="L7" s="12">
-        <f t="shared" si="4"/>
-        <v>2.0249190000000001</v>
-      </c>
-      <c r="M7" s="12">
-        <f t="shared" si="8"/>
-        <v>0.45</v>
-      </c>
-      <c r="N7" s="12">
-        <f t="shared" si="9"/>
-        <v>0.24999000000000002</v>
-      </c>
-      <c r="O7" s="12"/>
+      <c r="K7" s="11">
+        <f t="shared" si="6"/>
+        <v>2.13</v>
+      </c>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11">
+        <f t="shared" si="7"/>
+        <v>0.3</v>
+      </c>
+      <c r="N7" s="11"/>
+      <c r="O7" s="11"/>
     </row>
     <row r="8" spans="1:18">
       <c r="A8">
         <v>4000</v>
       </c>
-      <c r="B8" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12">
+      <c r="B8" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11">
         <f t="shared" si="0"/>
-        <v>0.25</v>
-      </c>
-      <c r="F8" s="12">
-        <f t="shared" si="5"/>
-        <v>0.08</v>
-      </c>
-      <c r="G8" s="12">
-        <f t="shared" si="6"/>
+        <v>0.23</v>
+      </c>
+      <c r="F8" s="11">
+        <f t="shared" si="2"/>
+        <v>0.05</v>
+      </c>
+      <c r="G8" s="11">
+        <f t="shared" si="3"/>
         <v>0.81</v>
       </c>
-      <c r="H8" s="12">
-        <f t="shared" si="7"/>
+      <c r="H8" s="11">
+        <f t="shared" si="4"/>
         <v>0.1</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J8" s="12">
-        <f t="shared" si="2"/>
+      <c r="J8" s="11">
+        <f t="shared" si="5"/>
         <v>3333.2000000000003</v>
       </c>
-      <c r="K8" s="12">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="L8" s="12">
-        <f t="shared" si="4"/>
-        <v>2.6998920000000002</v>
-      </c>
-      <c r="M8" s="12">
-        <f t="shared" si="8"/>
-        <v>0.32</v>
-      </c>
-      <c r="N8" s="12">
-        <f t="shared" si="9"/>
-        <v>0.33332000000000006</v>
-      </c>
-      <c r="O8" s="12"/>
+      <c r="K8" s="11">
+        <f t="shared" si="6"/>
+        <v>0.92</v>
+      </c>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11">
+        <f t="shared" si="7"/>
+        <v>0.2</v>
+      </c>
+      <c r="N8" s="11"/>
+      <c r="O8" s="11"/>
     </row>
     <row r="9" spans="1:18">
       <c r="A9">
         <v>5000</v>
       </c>
-      <c r="B9" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12">
+      <c r="B9" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11">
         <f t="shared" si="0"/>
-        <v>0.53</v>
-      </c>
-      <c r="F9" s="12">
-        <f t="shared" si="5"/>
-        <v>0.04</v>
-      </c>
-      <c r="G9" s="12">
-        <f t="shared" si="6"/>
+        <v>0.51</v>
+      </c>
+      <c r="F9" s="11">
+        <f t="shared" si="2"/>
+        <v>0.06</v>
+      </c>
+      <c r="G9" s="11">
+        <f t="shared" si="3"/>
         <v>0.81</v>
       </c>
-      <c r="H9" s="12">
-        <f t="shared" si="7"/>
+      <c r="H9" s="11">
+        <f t="shared" si="4"/>
         <v>0.1</v>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J9" s="12">
-        <f t="shared" si="2"/>
+      <c r="J9" s="11">
+        <f t="shared" si="5"/>
         <v>4166.5</v>
       </c>
-      <c r="K9" s="12">
-        <f t="shared" si="3"/>
-        <v>2.65</v>
-      </c>
-      <c r="L9" s="12">
-        <f t="shared" si="4"/>
-        <v>3.3748650000000002</v>
-      </c>
-      <c r="M9" s="12">
-        <f t="shared" si="8"/>
-        <v>0.2</v>
-      </c>
-      <c r="N9" s="12">
-        <f t="shared" si="9"/>
-        <v>0.41665000000000002</v>
-      </c>
+      <c r="K9" s="11">
+        <f t="shared" si="6"/>
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11">
+        <f t="shared" si="7"/>
+        <v>0.3</v>
+      </c>
+      <c r="N9" s="11"/>
     </row>
     <row r="10" spans="1:18">
       <c r="A10">
         <v>6000</v>
       </c>
-      <c r="B10" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12">
+      <c r="B10" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11">
         <f t="shared" si="0"/>
-        <v>0.62</v>
-      </c>
-      <c r="F10" s="12">
-        <f t="shared" si="5"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="G10" s="12">
-        <f t="shared" si="6"/>
+        <v>0.61</v>
+      </c>
+      <c r="F10" s="11">
+        <f t="shared" si="2"/>
+        <v>0.09</v>
+      </c>
+      <c r="G10" s="11">
+        <f t="shared" si="3"/>
         <v>0.81</v>
       </c>
-      <c r="H10" s="12">
-        <f t="shared" si="7"/>
+      <c r="H10" s="11">
+        <f t="shared" si="4"/>
         <v>0.1</v>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J10" s="12">
-        <f t="shared" si="2"/>
+      <c r="J10" s="11">
+        <f t="shared" si="5"/>
         <v>4999.8</v>
       </c>
-      <c r="K10" s="12">
-        <f t="shared" si="3"/>
-        <v>3.72</v>
-      </c>
-      <c r="L10" s="12">
-        <f t="shared" si="4"/>
-        <v>4.0498380000000003</v>
-      </c>
-      <c r="M10" s="12">
-        <f t="shared" si="8"/>
-        <v>0.42000000000000004</v>
-      </c>
-      <c r="N10" s="12">
-        <f t="shared" si="9"/>
-        <v>0.49998000000000004</v>
-      </c>
+      <c r="K10" s="11">
+        <f t="shared" si="6"/>
+        <v>3.66</v>
+      </c>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11">
+        <f t="shared" si="7"/>
+        <v>0.54</v>
+      </c>
+      <c r="N10" s="11"/>
     </row>
     <row r="11" spans="1:18">
       <c r="A11">
         <v>7000</v>
       </c>
-      <c r="B11" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12">
+      <c r="B11" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11">
         <f t="shared" si="0"/>
-        <v>0.12</v>
-      </c>
-      <c r="F11" s="12">
-        <f t="shared" si="5"/>
-        <v>0.01</v>
-      </c>
-      <c r="G11" s="12">
-        <f t="shared" si="6"/>
+        <v>0.15</v>
+      </c>
+      <c r="F11" s="11">
+        <f t="shared" si="2"/>
+        <v>0.03</v>
+      </c>
+      <c r="G11" s="11">
+        <f t="shared" si="3"/>
         <v>0.81</v>
       </c>
-      <c r="H11" s="12">
-        <f t="shared" si="7"/>
+      <c r="H11" s="11">
+        <f t="shared" si="4"/>
         <v>0.1</v>
       </c>
-      <c r="I11" s="12">
+      <c r="I11" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J11" s="12">
-        <f t="shared" si="2"/>
+      <c r="J11" s="11">
+        <f t="shared" si="5"/>
         <v>5833.1</v>
       </c>
-      <c r="K11" s="12">
-        <f t="shared" si="3"/>
-        <v>0.84</v>
-      </c>
-      <c r="L11" s="12">
-        <f t="shared" si="4"/>
-        <v>4.7248110000000008</v>
-      </c>
-      <c r="M11" s="12">
-        <f t="shared" si="8"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="N11" s="12">
-        <f t="shared" si="9"/>
-        <v>0.58331000000000011</v>
-      </c>
+      <c r="K11" s="11">
+        <f t="shared" si="6"/>
+        <v>1.05</v>
+      </c>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11">
+        <f t="shared" si="7"/>
+        <v>0.21</v>
+      </c>
+      <c r="N11" s="11"/>
     </row>
     <row r="12" spans="1:18">
       <c r="A12">
         <v>8000</v>
       </c>
-      <c r="B12" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12">
+      <c r="B12" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11">
         <f t="shared" si="0"/>
-        <v>0.54</v>
-      </c>
-      <c r="F12" s="12">
-        <f t="shared" si="5"/>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="F12" s="11">
+        <f t="shared" si="2"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="G12" s="12">
-        <f t="shared" si="6"/>
+      <c r="G12" s="11">
+        <f t="shared" si="3"/>
         <v>0.81</v>
       </c>
-      <c r="H12" s="12">
-        <f t="shared" si="7"/>
+      <c r="H12" s="11">
+        <f t="shared" si="4"/>
         <v>0.1</v>
       </c>
-      <c r="I12" s="12">
+      <c r="I12" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J12" s="12">
-        <f t="shared" si="2"/>
+      <c r="J12" s="11">
+        <f t="shared" si="5"/>
         <v>6666.4000000000005</v>
       </c>
-      <c r="K12" s="12">
-        <f t="shared" si="3"/>
-        <v>4.32</v>
-      </c>
-      <c r="L12" s="12">
-        <f t="shared" si="4"/>
-        <v>5.3997840000000004</v>
-      </c>
-      <c r="M12" s="12">
-        <f t="shared" si="8"/>
+      <c r="K12" s="11">
+        <f t="shared" si="6"/>
+        <v>4.4800000000000004</v>
+      </c>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11">
+        <f t="shared" si="7"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="N12" s="12">
-        <f t="shared" si="9"/>
-        <v>0.66664000000000012</v>
-      </c>
+      <c r="N12" s="11"/>
     </row>
     <row r="13" spans="1:18">
       <c r="A13">
         <v>9000</v>
       </c>
-      <c r="B13" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12">
+      <c r="B13" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11">
         <f t="shared" si="0"/>
-        <v>0.68</v>
-      </c>
-      <c r="F13" s="12">
+        <v>0.66</v>
+      </c>
+      <c r="F13" s="11">
+        <f t="shared" si="2"/>
+        <v>0.04</v>
+      </c>
+      <c r="G13" s="11">
+        <f t="shared" si="3"/>
+        <v>0.81</v>
+      </c>
+      <c r="H13" s="11">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+      <c r="I13" s="11">
+        <f t="shared" si="1"/>
+        <v>0.79510000000000003</v>
+      </c>
+      <c r="J13" s="11">
         <f t="shared" si="5"/>
-        <v>0.05</v>
-      </c>
-      <c r="G13" s="12">
+        <v>343.80000000000013</v>
+      </c>
+      <c r="K13" s="11">
         <f t="shared" si="6"/>
-        <v>0.81</v>
-      </c>
-      <c r="H13" s="12">
+        <v>5.94</v>
+      </c>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11">
         <f t="shared" si="7"/>
-        <v>0.1</v>
-      </c>
-      <c r="I13" s="12">
-        <f t="shared" si="1"/>
-        <v>0.74129999999999996</v>
-      </c>
-      <c r="J13" s="12">
+        <v>0.36</v>
+      </c>
+      <c r="N13" s="11"/>
+      <c r="O13" s="11"/>
+      <c r="P13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
+      <c r="B14" s="15"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11" t="str">
         <f t="shared" si="2"/>
-        <v>828.00000000000068</v>
-      </c>
-      <c r="K13" s="12">
-        <f t="shared" si="3"/>
-        <v>6.12</v>
-      </c>
-      <c r="L13" s="12">
-        <f t="shared" si="4"/>
-        <v>0.67068000000000061</v>
-      </c>
-      <c r="M13" s="12">
-        <f t="shared" si="8"/>
-        <v>0.45</v>
-      </c>
-      <c r="N13" s="12">
-        <f t="shared" si="9"/>
-        <v>8.2800000000000068E-2</v>
-      </c>
-      <c r="O13" s="12"/>
-      <c r="P13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18">
-      <c r="B14" s="16"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12" t="str">
-        <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="12"/>
-      <c r="L14" s="12" t="str">
-        <f t="shared" si="4"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11" t="str">
+        <f t="shared" ref="L14:L23" si="8">IF(ISBLANK(A14), "", J14*G14/1000)</f>
         <v/>
       </c>
-      <c r="M14" s="12" t="str">
-        <f t="shared" si="8"/>
+      <c r="M14" s="11" t="str">
+        <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="N14" s="12" t="str">
-        <f t="shared" si="9"/>
+      <c r="N14" s="11" t="str">
+        <f t="shared" ref="N14:N23" si="9">IF(ISBLANK(A14), "", J14*H14/1000)</f>
         <v/>
       </c>
-      <c r="O14" s="12"/>
+      <c r="O14" s="11"/>
       <c r="P14" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="Q14" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="R14" t="s">
         <v>1</v>
@@ -1446,58 +1393,52 @@
       <c r="A15">
         <v>1000</v>
       </c>
-      <c r="B15" s="17" t="s">
-        <v>12</v>
+      <c r="B15" s="16" t="s">
+        <v>33</v>
       </c>
       <c r="C15">
         <v>0.5</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="11">
         <v>0.2</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="11">
         <f t="shared" ref="E15:E23" si="10">IF(ISBLANK(A15), "", VLOOKUP(B15, $P$20:$T$28, 2, FALSE))</f>
-        <v>0.68</v>
-      </c>
-      <c r="F15" s="12">
-        <f t="shared" si="5"/>
-        <v>0.05</v>
-      </c>
-      <c r="G15" s="12">
+        <v>0.66</v>
+      </c>
+      <c r="F15" s="11">
+        <f t="shared" si="2"/>
+        <v>0.04</v>
+      </c>
+      <c r="G15" s="11">
         <f>$Q$15</f>
         <v>0.81</v>
       </c>
-      <c r="H15" s="12">
-        <f t="shared" si="7"/>
+      <c r="H15" s="11">
+        <f t="shared" si="4"/>
         <v>0.1</v>
       </c>
-      <c r="I15" s="12">
+      <c r="I15" s="11">
         <f t="shared" ref="I15:I23" si="11">IF(ISBLANK(A15), "", IF(B15="act", $Q$5, 0))</f>
         <v>0</v>
       </c>
-      <c r="J15" s="12">
-        <f t="shared" si="2"/>
-        <v>833.29970000000003</v>
-      </c>
-      <c r="K15" s="12">
-        <f t="shared" ref="K15:K23" si="12">A15*E15/1000</f>
-        <v>0.68</v>
-      </c>
-      <c r="L15" s="12">
-        <f t="shared" si="4"/>
-        <v>0.67497275700000015</v>
-      </c>
-      <c r="M15" s="12">
-        <f t="shared" si="8"/>
-        <v>0.05</v>
-      </c>
-      <c r="N15" s="12">
+      <c r="J15" s="11">
+        <f t="shared" si="5"/>
+        <v>533.30000000000007</v>
+      </c>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11">
+        <f>IF(ISBLANK(A15), "", J15*G15/1000)</f>
+        <v>0.43197300000000005</v>
+      </c>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11">
         <f t="shared" si="9"/>
-        <v>8.3329970000000003E-2</v>
-      </c>
-      <c r="O15" s="12"/>
+        <v>5.3330000000000009E-2</v>
+      </c>
+      <c r="O15" s="11"/>
       <c r="P15" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q15">
         <v>0.81</v>
@@ -1508,1049 +1449,937 @@
     </row>
     <row r="16" spans="1:18">
       <c r="A16">
-        <v>2000</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>13</v>
+        <v>4000</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>34</v>
       </c>
       <c r="C16">
-        <v>500</v>
-      </c>
-      <c r="D16" s="12">
-        <v>200</v>
-      </c>
-      <c r="E16" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="D16" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="E16" s="11">
         <f t="shared" si="10"/>
-        <v>0.79</v>
-      </c>
-      <c r="F16" s="12">
-        <f t="shared" si="5"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="G16" s="12">
-        <f t="shared" ref="G16:G23" si="13">$Q$15</f>
+        <v>0.77</v>
+      </c>
+      <c r="F16" s="11">
+        <f t="shared" si="2"/>
+        <v>0.09</v>
+      </c>
+      <c r="G16" s="11">
+        <f t="shared" ref="G16:G23" si="12">$Q$15</f>
         <v>0.81</v>
       </c>
-      <c r="H16" s="12">
-        <f t="shared" si="7"/>
+      <c r="H16" s="11">
+        <f t="shared" si="4"/>
         <v>0.1</v>
       </c>
-      <c r="I16" s="12">
+      <c r="I16" s="11">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J16" s="12">
-        <f t="shared" si="2"/>
-        <v>1666.3000000000002</v>
-      </c>
-      <c r="K16" s="12">
-        <f t="shared" si="12"/>
-        <v>1.58</v>
-      </c>
-      <c r="L16" s="12">
-        <f t="shared" si="4"/>
-        <v>1.3497030000000001</v>
-      </c>
-      <c r="M16" s="12">
+      <c r="J16" s="11">
+        <f>A16*(1-($Q$4+I16))-((C16-D16)*1000)</f>
+        <v>3133.2000000000003</v>
+      </c>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11">
         <f t="shared" si="8"/>
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="N16" s="12">
+        <v>2.5378920000000003</v>
+      </c>
+      <c r="M16" s="11"/>
+      <c r="N16" s="11">
         <f t="shared" si="9"/>
-        <v>0.16663000000000003</v>
-      </c>
-      <c r="O16" s="12"/>
+        <v>0.31332000000000004</v>
+      </c>
+      <c r="O16" s="11"/>
     </row>
     <row r="17" spans="1:23">
       <c r="A17">
         <v>3000</v>
       </c>
-      <c r="B17" s="17" t="s">
-        <v>14</v>
+      <c r="B17" s="16" t="s">
+        <v>35</v>
       </c>
       <c r="C17">
-        <v>400</v>
-      </c>
-      <c r="D17" s="12">
-        <v>200</v>
-      </c>
-      <c r="E17" s="12">
+        <v>0.4</v>
+      </c>
+      <c r="D17" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="E17" s="11">
         <f t="shared" si="10"/>
-        <v>0.73</v>
-      </c>
-      <c r="F17" s="12">
-        <f t="shared" si="5"/>
-        <v>0.15</v>
-      </c>
-      <c r="G17" s="12">
-        <f t="shared" si="13"/>
+        <v>0.71</v>
+      </c>
+      <c r="F17" s="11">
+        <f t="shared" si="2"/>
+        <v>0.1</v>
+      </c>
+      <c r="G17" s="11">
+        <f t="shared" si="12"/>
         <v>0.81</v>
       </c>
-      <c r="H17" s="12">
-        <f t="shared" si="7"/>
+      <c r="H17" s="11">
+        <f t="shared" si="4"/>
         <v>0.1</v>
       </c>
-      <c r="I17" s="12">
+      <c r="I17" s="11">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J17" s="12">
-        <f t="shared" si="2"/>
-        <v>2499.7000000000003</v>
-      </c>
-      <c r="K17" s="12">
-        <f t="shared" si="12"/>
-        <v>2.19</v>
-      </c>
-      <c r="L17" s="12">
-        <f t="shared" si="4"/>
-        <v>2.0247570000000001</v>
-      </c>
-      <c r="M17" s="12">
+      <c r="J17" s="11">
+        <f t="shared" si="5"/>
+        <v>2299.9</v>
+      </c>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11">
         <f t="shared" si="8"/>
-        <v>0.45</v>
-      </c>
-      <c r="N17" s="12">
+        <v>1.862919</v>
+      </c>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11">
         <f t="shared" si="9"/>
-        <v>0.24997000000000003</v>
-      </c>
-      <c r="O17" s="12"/>
+        <v>0.22999</v>
+      </c>
+      <c r="O17" s="11"/>
     </row>
     <row r="18" spans="1:23">
       <c r="A18">
         <v>4000</v>
       </c>
-      <c r="B18" s="17" t="s">
-        <v>15</v>
+      <c r="B18" s="16" t="s">
+        <v>36</v>
       </c>
       <c r="C18">
-        <v>10</v>
-      </c>
-      <c r="D18" s="12">
-        <v>5</v>
-      </c>
-      <c r="E18" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="D18" s="11">
+        <v>0.9</v>
+      </c>
+      <c r="E18" s="11">
         <f t="shared" si="10"/>
-        <v>0.25</v>
-      </c>
-      <c r="F18" s="12">
-        <f t="shared" si="5"/>
-        <v>0.08</v>
-      </c>
-      <c r="G18" s="12">
-        <f t="shared" si="13"/>
+        <v>0.23</v>
+      </c>
+      <c r="F18" s="11">
+        <f t="shared" si="2"/>
+        <v>0.05</v>
+      </c>
+      <c r="G18" s="11">
+        <f t="shared" si="12"/>
         <v>0.81</v>
       </c>
-      <c r="H18" s="12">
-        <f t="shared" si="7"/>
+      <c r="H18" s="11">
+        <f t="shared" si="4"/>
         <v>0.1</v>
       </c>
-      <c r="I18" s="12">
+      <c r="I18" s="11">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J18" s="12">
-        <f t="shared" si="2"/>
-        <v>3333.1950000000002</v>
-      </c>
-      <c r="K18" s="12">
-        <f t="shared" si="12"/>
-        <v>1</v>
-      </c>
-      <c r="L18" s="12">
-        <f t="shared" si="4"/>
-        <v>2.6998879500000004</v>
-      </c>
-      <c r="M18" s="12">
+      <c r="J18" s="11">
+        <f t="shared" si="5"/>
+        <v>4133.2000000000007</v>
+      </c>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11">
         <f t="shared" si="8"/>
-        <v>0.32</v>
-      </c>
-      <c r="N18" s="12">
+        <v>3.3478920000000008</v>
+      </c>
+      <c r="M18" s="11"/>
+      <c r="N18" s="11">
         <f t="shared" si="9"/>
-        <v>0.33331950000000005</v>
-      </c>
-      <c r="O18" s="12"/>
+        <v>0.41332000000000013</v>
+      </c>
+      <c r="O18" s="11"/>
     </row>
     <row r="19" spans="1:23" ht="68">
       <c r="A19">
         <v>5000</v>
       </c>
-      <c r="B19" s="17" t="s">
-        <v>16</v>
+      <c r="B19" s="16" t="s">
+        <v>37</v>
       </c>
       <c r="C19">
-        <v>1009</v>
-      </c>
-      <c r="D19" s="12">
-        <v>900</v>
-      </c>
-      <c r="E19" s="12">
+        <v>1.9</v>
+      </c>
+      <c r="D19" s="11">
+        <v>0.9</v>
+      </c>
+      <c r="E19" s="11">
         <f t="shared" si="10"/>
-        <v>0.53</v>
-      </c>
-      <c r="F19" s="12">
-        <f t="shared" si="5"/>
-        <v>0.04</v>
-      </c>
-      <c r="G19" s="12">
-        <f t="shared" si="13"/>
+        <v>0.51</v>
+      </c>
+      <c r="F19" s="11">
+        <f t="shared" si="2"/>
+        <v>0.06</v>
+      </c>
+      <c r="G19" s="11">
+        <f t="shared" si="12"/>
         <v>0.81</v>
       </c>
-      <c r="H19" s="12">
-        <f t="shared" si="7"/>
+      <c r="H19" s="11">
+        <f t="shared" si="4"/>
         <v>0.1</v>
       </c>
-      <c r="I19" s="12">
+      <c r="I19" s="11">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J19" s="12">
-        <f t="shared" si="2"/>
-        <v>4166.3909999999996</v>
-      </c>
-      <c r="K19" s="12">
-        <f t="shared" si="12"/>
-        <v>2.65</v>
-      </c>
-      <c r="L19" s="12">
-        <f t="shared" si="4"/>
-        <v>3.3747767099999999</v>
-      </c>
-      <c r="M19" s="12">
+      <c r="J19" s="11">
+        <f t="shared" si="5"/>
+        <v>3166.5</v>
+      </c>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11">
         <f t="shared" si="8"/>
-        <v>0.2</v>
-      </c>
-      <c r="N19" s="12">
+        <v>2.5648650000000002</v>
+      </c>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11">
         <f t="shared" si="9"/>
-        <v>0.41663909999999998</v>
-      </c>
-      <c r="O19" s="12"/>
-      <c r="P19" s="18" t="s">
+        <v>0.31665000000000004</v>
+      </c>
+      <c r="O19" s="11"/>
+      <c r="P19" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="Q19" s="7" t="s">
+      <c r="Q19" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="R19" s="7" t="s">
+      <c r="R19" s="6"/>
+      <c r="S19" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="S19" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="T19" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="W19" s="7"/>
+      <c r="T19" s="6"/>
+      <c r="W19" s="6"/>
     </row>
     <row r="20" spans="1:23">
       <c r="A20">
         <v>6000</v>
       </c>
-      <c r="B20" s="17" t="s">
-        <v>17</v>
+      <c r="B20" s="16" t="s">
+        <v>38</v>
       </c>
       <c r="C20">
-        <v>200</v>
-      </c>
-      <c r="D20" s="12">
-        <v>100</v>
-      </c>
-      <c r="E20" s="12">
+        <v>2.1</v>
+      </c>
+      <c r="D20" s="11">
+        <v>1</v>
+      </c>
+      <c r="E20" s="11">
         <f t="shared" si="10"/>
-        <v>0.62</v>
-      </c>
-      <c r="F20" s="12">
-        <f t="shared" si="5"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="G20" s="12">
-        <f t="shared" si="13"/>
+        <v>0.61</v>
+      </c>
+      <c r="F20" s="11">
+        <f t="shared" si="2"/>
+        <v>0.09</v>
+      </c>
+      <c r="G20" s="11">
+        <f t="shared" si="12"/>
         <v>0.81</v>
       </c>
-      <c r="H20" s="12">
-        <f t="shared" si="7"/>
+      <c r="H20" s="11">
+        <f t="shared" si="4"/>
         <v>0.1</v>
       </c>
-      <c r="I20" s="12">
+      <c r="I20" s="11">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J20" s="12">
-        <f t="shared" si="2"/>
-        <v>4999.7</v>
-      </c>
-      <c r="K20" s="12">
-        <f t="shared" si="12"/>
-        <v>3.72</v>
-      </c>
-      <c r="L20" s="12">
-        <f t="shared" si="4"/>
-        <v>4.0497570000000005</v>
-      </c>
-      <c r="M20" s="12">
+      <c r="J20" s="11">
+        <f t="shared" si="5"/>
+        <v>3899.8</v>
+      </c>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11">
         <f t="shared" si="8"/>
-        <v>0.42000000000000004</v>
-      </c>
-      <c r="N20" s="12">
+        <v>3.1588380000000003</v>
+      </c>
+      <c r="M20" s="11"/>
+      <c r="N20" s="11">
         <f t="shared" si="9"/>
-        <v>0.49997000000000003</v>
-      </c>
-      <c r="O20" s="12"/>
-      <c r="P20" s="17" t="s">
-        <v>12</v>
+        <v>0.38997999999999999</v>
+      </c>
+      <c r="O20" s="11"/>
+      <c r="P20" s="16" t="s">
+        <v>33</v>
       </c>
       <c r="Q20">
-        <v>0.68</v>
-      </c>
-      <c r="R20">
-        <v>188</v>
+        <v>0.66</v>
       </c>
       <c r="S20">
-        <v>0.05</v>
-      </c>
-      <c r="T20">
-        <v>15</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="21" spans="1:23">
       <c r="A21">
         <v>7000</v>
       </c>
-      <c r="B21" s="17" t="s">
-        <v>18</v>
+      <c r="B21" s="16" t="s">
+        <v>39</v>
       </c>
       <c r="C21">
-        <v>300</v>
-      </c>
-      <c r="D21" s="12">
-        <v>200</v>
-      </c>
-      <c r="E21" s="12">
+        <v>3</v>
+      </c>
+      <c r="D21" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="E21" s="11">
         <f t="shared" si="10"/>
-        <v>0.12</v>
-      </c>
-      <c r="F21" s="12">
-        <f t="shared" si="5"/>
-        <v>0.01</v>
-      </c>
-      <c r="G21" s="12">
-        <f t="shared" si="13"/>
+        <v>0.15</v>
+      </c>
+      <c r="F21" s="11">
+        <f t="shared" si="2"/>
+        <v>0.03</v>
+      </c>
+      <c r="G21" s="11">
+        <f t="shared" si="12"/>
         <v>0.81</v>
       </c>
-      <c r="H21" s="12">
-        <f t="shared" si="7"/>
+      <c r="H21" s="11">
+        <f t="shared" si="4"/>
         <v>0.1</v>
       </c>
-      <c r="I21" s="12">
+      <c r="I21" s="11">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J21" s="12">
-        <f t="shared" si="2"/>
-        <v>5833</v>
-      </c>
-      <c r="K21" s="12">
-        <f t="shared" si="12"/>
-        <v>0.84</v>
-      </c>
-      <c r="L21" s="12">
-        <f t="shared" si="4"/>
-        <v>4.7247300000000001</v>
-      </c>
-      <c r="M21" s="12">
+      <c r="J21" s="11">
+        <f t="shared" si="5"/>
+        <v>5333.1</v>
+      </c>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11">
         <f t="shared" si="8"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="N21" s="12">
+        <v>4.3198110000000005</v>
+      </c>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11">
         <f t="shared" si="9"/>
-        <v>0.58330000000000004</v>
-      </c>
-      <c r="O21" s="12"/>
-      <c r="P21" s="17" t="s">
-        <v>33</v>
+        <v>0.53331000000000006</v>
+      </c>
+      <c r="O21" s="11"/>
+      <c r="P21" s="16" t="s">
+        <v>41</v>
       </c>
       <c r="Q21">
-        <v>0.68</v>
-      </c>
-      <c r="R21">
-        <v>188</v>
+        <v>0.66</v>
       </c>
       <c r="S21">
-        <v>0.05</v>
-      </c>
-      <c r="T21">
-        <v>15</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="22" spans="1:23">
       <c r="A22">
         <v>8000</v>
       </c>
-      <c r="B22" s="17" t="s">
-        <v>19</v>
+      <c r="B22" s="16" t="s">
+        <v>40</v>
       </c>
       <c r="C22">
-        <v>400</v>
-      </c>
-      <c r="D22" s="12">
-        <v>20</v>
-      </c>
-      <c r="E22" s="12">
+        <v>4</v>
+      </c>
+      <c r="D22" s="11">
+        <v>2</v>
+      </c>
+      <c r="E22" s="11">
         <f t="shared" si="10"/>
-        <v>0.54</v>
-      </c>
-      <c r="F22" s="12">
-        <f t="shared" si="5"/>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="F22" s="11">
+        <f t="shared" si="2"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="G22" s="12">
-        <f t="shared" si="13"/>
+      <c r="G22" s="11">
+        <f t="shared" si="12"/>
         <v>0.81</v>
       </c>
-      <c r="H22" s="12">
-        <f t="shared" si="7"/>
+      <c r="H22" s="11">
+        <f t="shared" si="4"/>
         <v>0.1</v>
       </c>
-      <c r="I22" s="12">
+      <c r="I22" s="11">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J22" s="12">
-        <f t="shared" si="2"/>
-        <v>6666.02</v>
-      </c>
-      <c r="K22" s="12">
-        <f t="shared" si="12"/>
-        <v>4.32</v>
-      </c>
-      <c r="L22" s="12">
-        <f t="shared" si="4"/>
-        <v>5.3994762000000014</v>
-      </c>
-      <c r="M22" s="12">
+      <c r="J22" s="11">
+        <f t="shared" si="5"/>
+        <v>4666.4000000000005</v>
+      </c>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11">
         <f t="shared" si="8"/>
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="N22" s="12">
+        <v>3.7797840000000007</v>
+      </c>
+      <c r="M22" s="11"/>
+      <c r="N22" s="11">
         <f t="shared" si="9"/>
-        <v>0.66660200000000014</v>
-      </c>
-      <c r="P22" s="17" t="s">
-        <v>13</v>
+        <v>0.46664000000000011</v>
+      </c>
+      <c r="P22" s="16" t="s">
+        <v>34</v>
       </c>
       <c r="Q22">
-        <v>0.79</v>
-      </c>
-      <c r="R22">
-        <v>220</v>
+        <v>0.77</v>
       </c>
       <c r="S22">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="T22">
-        <v>18</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="23" spans="1:23">
       <c r="A23">
         <v>9000</v>
       </c>
-      <c r="B23" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="C23" s="12">
-        <v>500</v>
-      </c>
-      <c r="D23" s="12">
-        <v>200</v>
-      </c>
-      <c r="E23" s="12">
+      <c r="B23" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D23" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="E23" s="11">
         <f t="shared" si="10"/>
-        <v>0.68</v>
-      </c>
-      <c r="F23" s="12">
+        <v>0.66</v>
+      </c>
+      <c r="F23" s="11">
+        <f t="shared" si="2"/>
+        <v>0.04</v>
+      </c>
+      <c r="G23" s="11">
+        <f t="shared" si="12"/>
+        <v>0.81</v>
+      </c>
+      <c r="H23" s="11">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+      <c r="I23" s="11">
+        <f t="shared" si="11"/>
+        <v>0.79510000000000003</v>
+      </c>
+      <c r="J23" s="11">
         <f t="shared" si="5"/>
+        <v>43.800000000000125</v>
+      </c>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11">
+        <f t="shared" si="8"/>
+        <v>3.54780000000001E-2</v>
+      </c>
+      <c r="M23" s="11"/>
+      <c r="N23" s="11">
+        <f t="shared" si="9"/>
+        <v>4.3800000000000124E-3</v>
+      </c>
+      <c r="P23" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q23">
+        <v>0.71</v>
+      </c>
+      <c r="S23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23">
+      <c r="P24" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q24">
+        <v>0.23</v>
+      </c>
+      <c r="S24">
         <v>0.05</v>
       </c>
-      <c r="G23" s="12">
-        <f t="shared" si="13"/>
-        <v>0.81</v>
-      </c>
-      <c r="H23" s="12">
-        <f t="shared" si="7"/>
-        <v>0.1</v>
-      </c>
-      <c r="I23" s="12">
-        <f t="shared" si="11"/>
-        <v>0.74129999999999996</v>
-      </c>
-      <c r="J23" s="12">
-        <f t="shared" si="2"/>
-        <v>827.70000000000073</v>
-      </c>
-      <c r="K23" s="12">
-        <f t="shared" si="12"/>
-        <v>6.12</v>
-      </c>
-      <c r="L23" s="12">
-        <f t="shared" si="4"/>
-        <v>0.67043700000000062</v>
-      </c>
-      <c r="M23" s="12">
-        <f t="shared" si="8"/>
-        <v>0.45</v>
-      </c>
-      <c r="N23" s="12">
-        <f t="shared" si="9"/>
-        <v>8.277000000000008E-2</v>
-      </c>
-      <c r="P23" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q23">
-        <v>0.73</v>
-      </c>
-      <c r="R23">
-        <v>204</v>
-      </c>
-      <c r="S23">
+    </row>
+    <row r="25" spans="1:23">
+      <c r="O25" s="11"/>
+      <c r="P25" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q25">
+        <v>0.51</v>
+      </c>
+      <c r="S25">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23">
+      <c r="O26" s="11"/>
+      <c r="P26" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q26">
+        <v>0.61</v>
+      </c>
+      <c r="S26">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23">
+      <c r="O27" s="11"/>
+      <c r="P27" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q27">
         <v>0.15</v>
       </c>
-      <c r="T23">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="24" spans="1:23">
-      <c r="P24" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q24">
-        <v>0.25</v>
-      </c>
-      <c r="R24">
-        <v>71</v>
-      </c>
-      <c r="S24">
-        <v>0.08</v>
-      </c>
-      <c r="T24">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" spans="1:23">
-      <c r="O25" s="12"/>
-      <c r="P25" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q25">
-        <v>0.53</v>
-      </c>
-      <c r="R25">
-        <v>147</v>
-      </c>
-      <c r="S25">
-        <v>0.04</v>
-      </c>
-      <c r="T25">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:23">
-      <c r="O26" s="12"/>
-      <c r="P26" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q26">
-        <v>0.62</v>
-      </c>
-      <c r="R26">
-        <v>173</v>
-      </c>
-      <c r="S26">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="T26">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="1:23">
-      <c r="O27" s="12"/>
-      <c r="P27" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q27">
-        <v>0.12</v>
-      </c>
-      <c r="R27">
-        <v>32</v>
-      </c>
       <c r="S27">
-        <v>0.01</v>
-      </c>
-      <c r="T27">
-        <v>2</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="28" spans="1:23">
-      <c r="O28" s="12"/>
-      <c r="P28" s="17" t="s">
-        <v>19</v>
+      <c r="O28" s="11"/>
+      <c r="P28" s="16" t="s">
+        <v>40</v>
       </c>
       <c r="Q28">
-        <v>0.54</v>
-      </c>
-      <c r="R28">
-        <v>149</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="S28">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="T28">
-        <v>19</v>
-      </c>
     </row>
     <row r="29" spans="1:23">
-      <c r="O29" s="12"/>
-      <c r="P29" s="17" t="s">
-        <v>11</v>
+      <c r="O29" s="11"/>
+      <c r="P29" s="16" t="s">
+        <v>9</v>
       </c>
       <c r="Q29">
-        <v>0.65</v>
-      </c>
-      <c r="R29">
-        <v>179</v>
+        <v>0.63</v>
       </c>
       <c r="S29">
-        <v>0.08</v>
-      </c>
-      <c r="T29">
-        <v>23</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="30" spans="1:23">
-      <c r="O30" s="12"/>
+      <c r="O30" s="11"/>
     </row>
     <row r="31" spans="1:23">
-      <c r="O31" s="12"/>
+      <c r="O31" s="11"/>
     </row>
     <row r="32" spans="1:23">
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="12"/>
-      <c r="J32" s="12"/>
-      <c r="K32" s="12"/>
-      <c r="L32" s="12"/>
-      <c r="M32" s="12"/>
-      <c r="N32" s="12"/>
-      <c r="O32" s="12"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="11"/>
+      <c r="N32" s="11"/>
+      <c r="O32" s="11"/>
       <c r="R32" s="2"/>
       <c r="S32" s="2"/>
     </row>
     <row r="33" spans="2:26">
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="12"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="12"/>
-      <c r="M33" s="12"/>
-      <c r="N33" s="12"/>
-      <c r="O33" s="12"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+      <c r="M33" s="11"/>
+      <c r="N33" s="11"/>
+      <c r="O33" s="11"/>
       <c r="R33" s="2"/>
       <c r="S33" s="2"/>
     </row>
     <row r="34" spans="2:26">
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="12"/>
-      <c r="J34" s="12"/>
-      <c r="K34" s="12"/>
-      <c r="L34" s="12"/>
-      <c r="M34" s="12"/>
-      <c r="N34" s="12"/>
-      <c r="O34" s="12"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
+      <c r="N34" s="11"/>
+      <c r="O34" s="11"/>
     </row>
     <row r="35" spans="2:26">
-      <c r="C35" s="12"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="19"/>
-      <c r="H35" s="19"/>
-      <c r="I35" s="12"/>
-      <c r="J35" s="12"/>
-      <c r="K35" s="12"/>
-      <c r="L35" s="12"/>
-      <c r="M35" s="12"/>
-      <c r="N35" s="12"/>
-      <c r="O35" s="12"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="18"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="11"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="11"/>
+      <c r="L35" s="11"/>
+      <c r="M35" s="11"/>
+      <c r="N35" s="11"/>
+      <c r="O35" s="11"/>
       <c r="R35" s="2"/>
       <c r="S35" s="2"/>
-      <c r="T35" s="8"/>
+      <c r="T35" s="7"/>
     </row>
     <row r="36" spans="2:26">
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="12"/>
-      <c r="H36" s="12"/>
-      <c r="I36" s="12"/>
-      <c r="J36" s="12"/>
-      <c r="K36" s="12"/>
-      <c r="L36" s="12"/>
-      <c r="M36" s="12"/>
-      <c r="N36" s="12"/>
-      <c r="O36" s="12"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="7"/>
-      <c r="R36" s="14"/>
-      <c r="T36" s="14"/>
-      <c r="U36" s="15"/>
-      <c r="V36" s="7"/>
-      <c r="W36" s="7"/>
-      <c r="X36" s="7"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="11"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="11"/>
+      <c r="M36" s="11"/>
+      <c r="N36" s="11"/>
+      <c r="O36" s="11"/>
+      <c r="P36" s="6"/>
+      <c r="Q36" s="6"/>
+      <c r="R36" s="13"/>
+      <c r="T36" s="13"/>
+      <c r="U36" s="14"/>
+      <c r="V36" s="6"/>
+      <c r="W36" s="6"/>
+      <c r="X36" s="6"/>
     </row>
     <row r="37" spans="2:26">
-      <c r="B37" s="16"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="12"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
-      <c r="G37" s="12"/>
-      <c r="H37" s="12"/>
-      <c r="I37" s="12"/>
-      <c r="J37" s="12"/>
-      <c r="K37" s="12"/>
-      <c r="L37" s="12"/>
-      <c r="M37" s="12"/>
-      <c r="N37" s="12"/>
-      <c r="O37" s="12"/>
+      <c r="B37" s="15"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="11"/>
+      <c r="K37" s="11"/>
+      <c r="L37" s="11"/>
+      <c r="M37" s="11"/>
+      <c r="N37" s="11"/>
+      <c r="O37" s="11"/>
       <c r="R37" s="2"/>
       <c r="T37" s="2"/>
-      <c r="U37" s="8"/>
+      <c r="U37" s="7"/>
     </row>
     <row r="38" spans="2:26">
-      <c r="B38" s="16"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="12"/>
-      <c r="E38" s="12"/>
-      <c r="F38" s="12"/>
-      <c r="G38" s="12"/>
-      <c r="H38" s="12"/>
-      <c r="I38" s="12"/>
-      <c r="J38" s="12"/>
-      <c r="K38" s="12"/>
-      <c r="L38" s="12"/>
-      <c r="M38" s="12"/>
-      <c r="N38" s="12"/>
-      <c r="O38" s="12"/>
+      <c r="B38" s="15"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
+      <c r="J38" s="11"/>
+      <c r="K38" s="11"/>
+      <c r="L38" s="11"/>
+      <c r="M38" s="11"/>
+      <c r="N38" s="11"/>
+      <c r="O38" s="11"/>
     </row>
     <row r="39" spans="2:26">
-      <c r="B39" s="16"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="12"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="12"/>
-      <c r="H39" s="12"/>
-      <c r="I39" s="12"/>
-      <c r="J39" s="12"/>
-      <c r="K39" s="12"/>
-      <c r="L39" s="12"/>
-      <c r="M39" s="12"/>
-      <c r="N39" s="12"/>
-      <c r="O39" s="12"/>
+      <c r="B39" s="15"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="11"/>
+      <c r="J39" s="11"/>
+      <c r="K39" s="11"/>
+      <c r="L39" s="11"/>
+      <c r="M39" s="11"/>
+      <c r="N39" s="11"/>
+      <c r="O39" s="11"/>
       <c r="R39" s="2"/>
       <c r="T39" s="2"/>
     </row>
     <row r="40" spans="2:26">
-      <c r="C40" s="12"/>
-      <c r="D40" s="12"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12"/>
-      <c r="G40" s="12"/>
-      <c r="H40" s="12"/>
-      <c r="I40" s="12"/>
-      <c r="J40" s="12"/>
-      <c r="K40" s="12"/>
-      <c r="L40" s="12"/>
-      <c r="M40" s="12"/>
-      <c r="N40" s="12"/>
-      <c r="O40" s="12"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="11"/>
+      <c r="J40" s="11"/>
+      <c r="K40" s="11"/>
+      <c r="L40" s="11"/>
+      <c r="M40" s="11"/>
+      <c r="N40" s="11"/>
+      <c r="O40" s="11"/>
       <c r="R40" s="2"/>
       <c r="T40" s="2"/>
     </row>
     <row r="41" spans="2:26">
-      <c r="C41" s="12"/>
-      <c r="D41" s="12"/>
-      <c r="E41" s="12"/>
-      <c r="F41" s="12"/>
-      <c r="G41" s="12"/>
-      <c r="H41" s="12"/>
-      <c r="I41" s="12"/>
-      <c r="J41" s="12"/>
-      <c r="K41" s="12"/>
-      <c r="L41" s="12"/>
-      <c r="M41" s="12"/>
-      <c r="N41" s="12"/>
-      <c r="O41" s="12"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="11"/>
+      <c r="J41" s="11"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="11"/>
+      <c r="M41" s="11"/>
+      <c r="N41" s="11"/>
+      <c r="O41" s="11"/>
       <c r="R41" s="2"/>
       <c r="T41" s="2"/>
-      <c r="W41" s="7"/>
+      <c r="W41" s="6"/>
     </row>
     <row r="42" spans="2:26">
-      <c r="C42" s="12"/>
-      <c r="D42" s="12"/>
-      <c r="E42" s="12"/>
-      <c r="F42" s="12"/>
-      <c r="G42" s="12"/>
-      <c r="H42" s="12"/>
-      <c r="I42" s="12"/>
-      <c r="J42" s="12"/>
-      <c r="K42" s="12"/>
-      <c r="L42" s="12"/>
-      <c r="M42" s="12"/>
-      <c r="N42" s="12"/>
-      <c r="O42" s="12"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
+      <c r="F42" s="11"/>
+      <c r="G42" s="11"/>
+      <c r="H42" s="11"/>
+      <c r="I42" s="11"/>
+      <c r="J42" s="11"/>
+      <c r="K42" s="11"/>
+      <c r="L42" s="11"/>
+      <c r="M42" s="11"/>
+      <c r="N42" s="11"/>
+      <c r="O42" s="11"/>
       <c r="R42" s="2"/>
       <c r="T42" s="2"/>
-      <c r="W42" s="7"/>
+      <c r="W42" s="6"/>
     </row>
     <row r="43" spans="2:26">
-      <c r="C43" s="12"/>
-      <c r="D43" s="12"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="12"/>
-      <c r="G43" s="12"/>
-      <c r="H43" s="12"/>
-      <c r="I43" s="12"/>
-      <c r="J43" s="12"/>
-      <c r="K43" s="12"/>
-      <c r="L43" s="12"/>
-      <c r="M43" s="12"/>
-      <c r="N43" s="12"/>
-      <c r="O43" s="12"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="11"/>
+      <c r="J43" s="11"/>
+      <c r="K43" s="11"/>
+      <c r="L43" s="11"/>
+      <c r="M43" s="11"/>
+      <c r="N43" s="11"/>
+      <c r="O43" s="11"/>
       <c r="R43" s="2"/>
-      <c r="T43" s="11"/>
-      <c r="U43" s="10"/>
-      <c r="V43" s="10"/>
-      <c r="W43" s="10"/>
-      <c r="X43" s="10"/>
-      <c r="Y43" s="10"/>
-      <c r="Z43" s="10"/>
+      <c r="T43" s="10"/>
+      <c r="U43" s="9"/>
+      <c r="V43" s="9"/>
+      <c r="W43" s="9"/>
+      <c r="X43" s="9"/>
+      <c r="Y43" s="9"/>
+      <c r="Z43" s="9"/>
     </row>
     <row r="44" spans="2:26">
       <c r="R44" s="2"/>
-      <c r="T44" s="11"/>
-      <c r="U44" s="10"/>
-      <c r="V44" s="10"/>
-      <c r="W44" s="10"/>
-      <c r="X44" s="10"/>
-      <c r="Y44" s="10"/>
-      <c r="Z44" s="10"/>
+      <c r="T44" s="10"/>
+      <c r="U44" s="9"/>
+      <c r="V44" s="9"/>
+      <c r="W44" s="9"/>
+      <c r="X44" s="9"/>
+      <c r="Y44" s="9"/>
+      <c r="Z44" s="9"/>
     </row>
     <row r="45" spans="2:26">
       <c r="R45" s="2"/>
       <c r="T45" s="2"/>
-      <c r="U45" s="8"/>
-      <c r="Y45" s="10"/>
-      <c r="Z45" s="10"/>
+      <c r="U45" s="7"/>
+      <c r="Y45" s="9"/>
+      <c r="Z45" s="9"/>
     </row>
     <row r="46" spans="2:26">
-      <c r="Y46" s="10"/>
-      <c r="Z46" s="10"/>
+      <c r="Y46" s="9"/>
+      <c r="Z46" s="9"/>
     </row>
     <row r="47" spans="2:26">
       <c r="R47" s="2"/>
       <c r="T47" s="2"/>
-      <c r="Y47" s="10"/>
-      <c r="Z47" s="10"/>
+      <c r="Y47" s="9"/>
+      <c r="Z47" s="9"/>
     </row>
     <row r="48" spans="2:26">
       <c r="R48" s="2"/>
       <c r="T48" s="2"/>
-      <c r="W48" s="7"/>
-      <c r="Y48" s="10"/>
-      <c r="Z48" s="10"/>
+      <c r="W48" s="6"/>
+      <c r="Y48" s="9"/>
+      <c r="Z48" s="9"/>
     </row>
     <row r="49" spans="18:26">
       <c r="R49" s="2"/>
-      <c r="T49" s="11"/>
-      <c r="U49" s="10"/>
-      <c r="V49" s="10"/>
-      <c r="W49" s="10"/>
-      <c r="X49" s="10"/>
-      <c r="Y49" s="10"/>
-      <c r="Z49" s="10"/>
+      <c r="T49" s="10"/>
+      <c r="U49" s="9"/>
+      <c r="V49" s="9"/>
+      <c r="W49" s="9"/>
+      <c r="X49" s="9"/>
+      <c r="Y49" s="9"/>
+      <c r="Z49" s="9"/>
     </row>
     <row r="50" spans="18:26">
       <c r="R50" s="2"/>
-      <c r="T50" s="11"/>
-      <c r="U50" s="10"/>
-      <c r="V50" s="10"/>
-      <c r="W50" s="10"/>
-      <c r="X50" s="10"/>
-      <c r="Y50" s="10"/>
-      <c r="Z50" s="10"/>
+      <c r="T50" s="10"/>
+      <c r="U50" s="9"/>
+      <c r="V50" s="9"/>
+      <c r="W50" s="9"/>
+      <c r="X50" s="9"/>
+      <c r="Y50" s="9"/>
+      <c r="Z50" s="9"/>
     </row>
     <row r="51" spans="18:26">
       <c r="R51" s="2"/>
-      <c r="T51" s="11"/>
-      <c r="U51" s="10"/>
-      <c r="V51" s="10"/>
-      <c r="W51" s="10"/>
-      <c r="X51" s="10"/>
-      <c r="Y51" s="10"/>
-      <c r="Z51" s="10"/>
+      <c r="T51" s="10"/>
+      <c r="U51" s="9"/>
+      <c r="V51" s="9"/>
+      <c r="W51" s="9"/>
+      <c r="X51" s="9"/>
+      <c r="Y51" s="9"/>
+      <c r="Z51" s="9"/>
     </row>
     <row r="52" spans="18:26">
       <c r="R52" s="2"/>
-      <c r="T52" s="11"/>
-      <c r="U52" s="10"/>
-      <c r="V52" s="10"/>
-      <c r="W52" s="10"/>
-      <c r="X52" s="10"/>
-      <c r="Y52" s="10"/>
-      <c r="Z52" s="10"/>
+      <c r="T52" s="10"/>
+      <c r="U52" s="9"/>
+      <c r="V52" s="9"/>
+      <c r="W52" s="9"/>
+      <c r="X52" s="9"/>
+      <c r="Y52" s="9"/>
+      <c r="Z52" s="9"/>
     </row>
     <row r="53" spans="18:26">
       <c r="R53" s="2"/>
-      <c r="T53" s="11"/>
-      <c r="U53" s="10"/>
-      <c r="V53" s="10"/>
-      <c r="W53" s="10"/>
-      <c r="X53" s="10"/>
-      <c r="Y53" s="10"/>
-      <c r="Z53" s="10"/>
+      <c r="T53" s="10"/>
+      <c r="U53" s="9"/>
+      <c r="V53" s="9"/>
+      <c r="W53" s="9"/>
+      <c r="X53" s="9"/>
+      <c r="Y53" s="9"/>
+      <c r="Z53" s="9"/>
     </row>
     <row r="54" spans="18:26">
       <c r="R54" s="2"/>
-      <c r="T54" s="11"/>
-      <c r="U54" s="10"/>
-      <c r="V54" s="10"/>
-      <c r="W54" s="10"/>
-      <c r="X54" s="10"/>
-      <c r="Y54" s="10"/>
-      <c r="Z54" s="10"/>
+      <c r="T54" s="10"/>
+      <c r="U54" s="9"/>
+      <c r="V54" s="9"/>
+      <c r="W54" s="9"/>
+      <c r="X54" s="9"/>
+      <c r="Y54" s="9"/>
+      <c r="Z54" s="9"/>
     </row>
     <row r="55" spans="18:26">
       <c r="R55" s="2"/>
-      <c r="T55" s="11"/>
-      <c r="U55" s="10"/>
-      <c r="V55" s="10"/>
-      <c r="W55" s="10"/>
-      <c r="X55" s="10"/>
-      <c r="Y55" s="10"/>
-      <c r="Z55" s="10"/>
+      <c r="T55" s="10"/>
+      <c r="U55" s="9"/>
+      <c r="V55" s="9"/>
+      <c r="W55" s="9"/>
+      <c r="X55" s="9"/>
+      <c r="Y55" s="9"/>
+      <c r="Z55" s="9"/>
     </row>
     <row r="56" spans="18:26">
       <c r="R56" s="2"/>
-      <c r="T56" s="11"/>
-      <c r="U56" s="10"/>
-      <c r="V56" s="10"/>
-      <c r="W56" s="10"/>
-      <c r="X56" s="10"/>
-      <c r="Y56" s="10"/>
-      <c r="Z56" s="10"/>
+      <c r="T56" s="10"/>
+      <c r="U56" s="9"/>
+      <c r="V56" s="9"/>
+      <c r="W56" s="9"/>
+      <c r="X56" s="9"/>
+      <c r="Y56" s="9"/>
+      <c r="Z56" s="9"/>
     </row>
     <row r="57" spans="18:26">
       <c r="R57" s="2"/>
-      <c r="T57" s="11"/>
-      <c r="U57" s="10"/>
-      <c r="V57" s="10"/>
-      <c r="W57" s="10"/>
-      <c r="X57" s="10"/>
-      <c r="Y57" s="10"/>
-      <c r="Z57" s="10"/>
+      <c r="T57" s="10"/>
+      <c r="U57" s="9"/>
+      <c r="V57" s="9"/>
+      <c r="W57" s="9"/>
+      <c r="X57" s="9"/>
+      <c r="Y57" s="9"/>
+      <c r="Z57" s="9"/>
     </row>
     <row r="58" spans="18:26">
       <c r="R58" s="2"/>
-      <c r="T58" s="11"/>
-      <c r="U58" s="10"/>
-      <c r="V58" s="10"/>
-      <c r="W58" s="10"/>
-      <c r="X58" s="10"/>
-      <c r="Y58" s="10"/>
-      <c r="Z58" s="10"/>
+      <c r="T58" s="10"/>
+      <c r="U58" s="9"/>
+      <c r="V58" s="9"/>
+      <c r="W58" s="9"/>
+      <c r="X58" s="9"/>
+      <c r="Y58" s="9"/>
+      <c r="Z58" s="9"/>
     </row>
     <row r="59" spans="18:26">
       <c r="R59" s="2"/>
-      <c r="T59" s="11"/>
-      <c r="U59" s="10"/>
-      <c r="V59" s="10"/>
-      <c r="W59" s="10"/>
-      <c r="X59" s="10"/>
-      <c r="Y59" s="10"/>
-      <c r="Z59" s="10"/>
+      <c r="T59" s="10"/>
+      <c r="U59" s="9"/>
+      <c r="V59" s="9"/>
+      <c r="W59" s="9"/>
+      <c r="X59" s="9"/>
+      <c r="Y59" s="9"/>
+      <c r="Z59" s="9"/>
     </row>
     <row r="60" spans="18:26">
       <c r="R60" s="2"/>
-      <c r="T60" s="11"/>
-      <c r="U60" s="10"/>
-      <c r="V60" s="10"/>
-      <c r="W60" s="10"/>
-      <c r="X60" s="10"/>
-      <c r="Y60" s="10"/>
-      <c r="Z60" s="10"/>
+      <c r="T60" s="10"/>
+      <c r="U60" s="9"/>
+      <c r="V60" s="9"/>
+      <c r="W60" s="9"/>
+      <c r="X60" s="9"/>
+      <c r="Y60" s="9"/>
+      <c r="Z60" s="9"/>
     </row>
     <row r="61" spans="18:26">
       <c r="R61" s="2"/>
-      <c r="T61" s="11"/>
-      <c r="U61" s="10"/>
-      <c r="V61" s="10"/>
-      <c r="W61" s="10"/>
-      <c r="X61" s="10"/>
-      <c r="Y61" s="10"/>
-      <c r="Z61" s="10"/>
+      <c r="T61" s="10"/>
+      <c r="U61" s="9"/>
+      <c r="V61" s="9"/>
+      <c r="W61" s="9"/>
+      <c r="X61" s="9"/>
+      <c r="Y61" s="9"/>
+      <c r="Z61" s="9"/>
     </row>
     <row r="62" spans="18:26">
       <c r="R62" s="2"/>
-      <c r="T62" s="11"/>
-      <c r="U62" s="10"/>
-      <c r="V62" s="10"/>
-      <c r="W62" s="10"/>
-      <c r="X62" s="10"/>
-      <c r="Y62" s="10"/>
-      <c r="Z62" s="10"/>
+      <c r="T62" s="10"/>
+      <c r="U62" s="9"/>
+      <c r="V62" s="9"/>
+      <c r="W62" s="9"/>
+      <c r="X62" s="9"/>
+      <c r="Y62" s="9"/>
+      <c r="Z62" s="9"/>
     </row>
     <row r="63" spans="18:26">
       <c r="R63" s="2"/>
-      <c r="T63" s="11"/>
-      <c r="U63" s="10"/>
-      <c r="V63" s="10"/>
-      <c r="W63" s="10"/>
-      <c r="X63" s="10"/>
-      <c r="Y63" s="10"/>
-      <c r="Z63" s="10"/>
+      <c r="T63" s="10"/>
+      <c r="U63" s="9"/>
+      <c r="V63" s="9"/>
+      <c r="W63" s="9"/>
+      <c r="X63" s="9"/>
+      <c r="Y63" s="9"/>
+      <c r="Z63" s="9"/>
     </row>
     <row r="64" spans="18:26">
       <c r="R64" s="2"/>
-      <c r="T64" s="9"/>
-      <c r="U64" s="9"/>
-      <c r="V64" s="9"/>
-      <c r="X64" s="9"/>
-      <c r="Y64" s="9"/>
-      <c r="Z64" s="9"/>
+      <c r="T64" s="8"/>
+      <c r="U64" s="8"/>
+      <c r="V64" s="8"/>
+      <c r="X64" s="8"/>
+      <c r="Y64" s="8"/>
+      <c r="Z64" s="8"/>
     </row>
     <row r="65" spans="18:26">
       <c r="T65" s="2"/>
-      <c r="U65" s="11"/>
-      <c r="V65" s="10"/>
-      <c r="Y65" s="9"/>
-      <c r="Z65" s="9"/>
+      <c r="U65" s="10"/>
+      <c r="V65" s="9"/>
+      <c r="Y65" s="8"/>
+      <c r="Z65" s="8"/>
     </row>
     <row r="66" spans="18:26">
       <c r="T66" s="2"/>
@@ -2625,6 +2454,9 @@
       <c r="S84" s="2"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="R4" r:id="rId1" xr:uid="{11305529-0BBB-0D49-8333-C5A0E083BDF3}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/packages/calculators/src/modules/test/14-electricity.xlsx
+++ b/packages/calculators/src/modules/test/14-electricity.xlsx
@@ -3,11 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators-internal/packages/calculators/src/modules/test/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20066D07-B7A9-FD4E-8E1A-6773CAF67D66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="15900" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>

--- a/packages/calculators/src/modules/test/14-electricity.xlsx
+++ b/packages/calculators/src/modules/test/14-electricity.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators-internal/packages/calculators/src/modules/test/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mackcheesman/Desktop/Work/EAP/Code/emissions-calculators/packages/calculators/src/modules/test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20066D07-B7A9-FD4E-8E1A-6773CAF67D66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27BA3B66-F57E-3448-BA5C-F3FCD1B335D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="15900" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
   </bookViews>
@@ -957,19 +957,19 @@
       <c r="D5" s="11"/>
       <c r="E5" s="11">
         <f t="shared" ref="E5:E13" si="0">IF(ISBLANK(A5), "", VLOOKUP(B5, $P$20:$T$28, 2, FALSE))</f>
-        <v>0.66</v>
+        <v>0.6</v>
       </c>
       <c r="F5" s="11">
         <f>IF(ISBLANK(A5), "", VLOOKUP(B5, $P$20:$T$28, 4, FALSE))</f>
-        <v>0.04</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G5" s="11">
         <f>$Q$15</f>
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="H5" s="11">
         <f>$R$15</f>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I5" s="11">
         <f t="shared" ref="I5:I13" si="1">IF(ISBLANK(A5), "", IF(B5="act", $Q$5, 0))</f>
@@ -981,12 +981,12 @@
       </c>
       <c r="K5" s="11">
         <f>A5*E5/1000</f>
-        <v>0.66</v>
+        <v>0.6</v>
       </c>
       <c r="L5" s="11"/>
       <c r="M5" s="11">
         <f>IF(ISBLANK(A5), "", A5*F5/1000)</f>
-        <v>0.04</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="N5" s="11"/>
       <c r="O5" s="11"/>
@@ -1010,19 +1010,19 @@
       <c r="D6" s="11"/>
       <c r="E6" s="11">
         <f t="shared" si="0"/>
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="F6" s="11">
         <f t="shared" ref="F6:F23" si="2">IF(ISBLANK(A6), "", VLOOKUP(B6, $P$20:$T$28, 4, FALSE))</f>
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="G6" s="11">
         <f t="shared" ref="G6:G13" si="3">$Q$15</f>
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="H6" s="11">
         <f t="shared" ref="H6:H23" si="4">$R$15</f>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I6" s="11">
         <f t="shared" si="1"/>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="K6" s="11">
         <f t="shared" ref="K6:K13" si="6">A6*E6/1000</f>
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="L6" s="11"/>
       <c r="M6" s="11">
         <f t="shared" ref="M6:M14" si="7">IF(ISBLANK(A6), "", A6*F6/1000)</f>
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="N6" s="11"/>
       <c r="O6" s="11"/>
@@ -1054,19 +1054,19 @@
       <c r="D7" s="11"/>
       <c r="E7" s="11">
         <f t="shared" si="0"/>
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="F7" s="11">
         <f t="shared" si="2"/>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="G7" s="11">
         <f t="shared" si="3"/>
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="H7" s="11">
         <f t="shared" si="4"/>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I7" s="11">
         <f t="shared" si="1"/>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="K7" s="11">
         <f t="shared" si="6"/>
-        <v>2.13</v>
+        <v>1.95</v>
       </c>
       <c r="L7" s="11"/>
       <c r="M7" s="11">
         <f t="shared" si="7"/>
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="N7" s="11"/>
       <c r="O7" s="11"/>
@@ -1098,19 +1098,19 @@
       <c r="D8" s="11"/>
       <c r="E8" s="11">
         <f t="shared" si="0"/>
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="F8" s="11">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="G8" s="11">
         <f t="shared" si="3"/>
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="H8" s="11">
         <f t="shared" si="4"/>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I8" s="11">
         <f t="shared" si="1"/>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="K8" s="11">
         <f t="shared" si="6"/>
-        <v>0.92</v>
+        <v>0.84</v>
       </c>
       <c r="L8" s="11"/>
       <c r="M8" s="11">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="N8" s="11"/>
       <c r="O8" s="11"/>
@@ -1142,19 +1142,19 @@
       <c r="D9" s="11"/>
       <c r="E9" s="11">
         <f t="shared" si="0"/>
-        <v>0.51</v>
+        <v>0.45</v>
       </c>
       <c r="F9" s="11">
         <f t="shared" si="2"/>
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="G9" s="11">
         <f t="shared" si="3"/>
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="H9" s="11">
         <f t="shared" si="4"/>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I9" s="11">
         <f t="shared" si="1"/>
@@ -1166,12 +1166,12 @@
       </c>
       <c r="K9" s="11">
         <f t="shared" si="6"/>
-        <v>2.5499999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="L9" s="11"/>
       <c r="M9" s="11">
         <f t="shared" si="7"/>
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="N9" s="11"/>
     </row>
@@ -1185,7 +1185,7 @@
       <c r="D10" s="11"/>
       <c r="E10" s="11">
         <f t="shared" si="0"/>
-        <v>0.61</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="F10" s="11">
         <f t="shared" si="2"/>
@@ -1193,11 +1193,11 @@
       </c>
       <c r="G10" s="11">
         <f t="shared" si="3"/>
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="H10" s="11">
         <f t="shared" si="4"/>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I10" s="11">
         <f t="shared" si="1"/>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="K10" s="11">
         <f t="shared" si="6"/>
-        <v>3.66</v>
+        <v>3.3600000000000003</v>
       </c>
       <c r="L10" s="11"/>
       <c r="M10" s="11">
@@ -1228,7 +1228,7 @@
       <c r="D11" s="11"/>
       <c r="E11" s="11">
         <f t="shared" si="0"/>
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="F11" s="11">
         <f t="shared" si="2"/>
@@ -1236,11 +1236,11 @@
       </c>
       <c r="G11" s="11">
         <f t="shared" si="3"/>
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="H11" s="11">
         <f t="shared" si="4"/>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I11" s="11">
         <f t="shared" si="1"/>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="K11" s="11">
         <f t="shared" si="6"/>
-        <v>1.05</v>
+        <v>1.47</v>
       </c>
       <c r="L11" s="11"/>
       <c r="M11" s="11">
@@ -1271,19 +1271,19 @@
       <c r="D12" s="11"/>
       <c r="E12" s="11">
         <f t="shared" si="0"/>
-        <v>0.56000000000000005</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="F12" s="11">
         <f t="shared" si="2"/>
-        <v>7.0000000000000007E-2</v>
+        <v>0.13</v>
       </c>
       <c r="G12" s="11">
         <f t="shared" si="3"/>
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="H12" s="11">
         <f t="shared" si="4"/>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I12" s="11">
         <f t="shared" si="1"/>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="K12" s="11">
         <f t="shared" si="6"/>
-        <v>4.4800000000000004</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L12" s="11"/>
       <c r="M12" s="11">
         <f t="shared" si="7"/>
-        <v>0.56000000000000005</v>
+        <v>1.04</v>
       </c>
       <c r="N12" s="11"/>
     </row>
@@ -1315,19 +1315,19 @@
       <c r="D13" s="11"/>
       <c r="E13" s="11">
         <f t="shared" si="0"/>
-        <v>0.66</v>
+        <v>0.6</v>
       </c>
       <c r="F13" s="11">
         <f t="shared" si="2"/>
-        <v>0.04</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G13" s="11">
         <f t="shared" si="3"/>
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="H13" s="11">
         <f t="shared" si="4"/>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I13" s="11">
         <f t="shared" si="1"/>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="K13" s="11">
         <f t="shared" si="6"/>
-        <v>5.94</v>
+        <v>5.4</v>
       </c>
       <c r="L13" s="11"/>
       <c r="M13" s="11">
         <f t="shared" si="7"/>
-        <v>0.36</v>
+        <v>0.63000000000000012</v>
       </c>
       <c r="N13" s="11"/>
       <c r="O13" s="11"/>
@@ -1404,19 +1404,19 @@
       </c>
       <c r="E15" s="11">
         <f t="shared" ref="E15:E23" si="10">IF(ISBLANK(A15), "", VLOOKUP(B15, $P$20:$T$28, 2, FALSE))</f>
-        <v>0.66</v>
+        <v>0.6</v>
       </c>
       <c r="F15" s="11">
         <f t="shared" si="2"/>
-        <v>0.04</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G15" s="11">
         <f>$Q$15</f>
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="H15" s="11">
         <f t="shared" si="4"/>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I15" s="11">
         <f t="shared" ref="I15:I23" si="11">IF(ISBLANK(A15), "", IF(B15="act", $Q$5, 0))</f>
@@ -1429,22 +1429,22 @@
       <c r="K15" s="11"/>
       <c r="L15" s="11">
         <f>IF(ISBLANK(A15), "", J15*G15/1000)</f>
-        <v>0.43197300000000005</v>
+        <v>0.4213070000000001</v>
       </c>
       <c r="M15" s="11"/>
       <c r="N15" s="11">
         <f t="shared" si="9"/>
-        <v>5.3330000000000009E-2</v>
+        <v>5.8663000000000014E-2</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" t="s">
         <v>9</v>
       </c>
       <c r="Q15">
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="R15">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -1462,19 +1462,19 @@
       </c>
       <c r="E16" s="11">
         <f t="shared" si="10"/>
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="F16" s="11">
         <f t="shared" si="2"/>
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="G16" s="11">
         <f t="shared" ref="G16:G23" si="12">$Q$15</f>
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="H16" s="11">
         <f t="shared" si="4"/>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I16" s="11">
         <f t="shared" si="11"/>
@@ -1487,12 +1487,12 @@
       <c r="K16" s="11"/>
       <c r="L16" s="11">
         <f t="shared" si="8"/>
-        <v>2.5378920000000003</v>
+        <v>2.4752280000000004</v>
       </c>
       <c r="M16" s="11"/>
       <c r="N16" s="11">
         <f t="shared" si="9"/>
-        <v>0.31332000000000004</v>
+        <v>0.34465200000000007</v>
       </c>
       <c r="O16" s="11"/>
     </row>
@@ -1511,19 +1511,19 @@
       </c>
       <c r="E17" s="11">
         <f t="shared" si="10"/>
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="F17" s="11">
         <f t="shared" si="2"/>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="G17" s="11">
         <f t="shared" si="12"/>
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="H17" s="11">
         <f t="shared" si="4"/>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I17" s="11">
         <f t="shared" si="11"/>
@@ -1536,12 +1536,12 @@
       <c r="K17" s="11"/>
       <c r="L17" s="11">
         <f t="shared" si="8"/>
-        <v>1.862919</v>
+        <v>1.816921</v>
       </c>
       <c r="M17" s="11"/>
       <c r="N17" s="11">
         <f t="shared" si="9"/>
-        <v>0.22999</v>
+        <v>0.25298900000000002</v>
       </c>
       <c r="O17" s="11"/>
     </row>
@@ -1560,19 +1560,19 @@
       </c>
       <c r="E18" s="11">
         <f t="shared" si="10"/>
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="F18" s="11">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="G18" s="11">
         <f t="shared" si="12"/>
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="H18" s="11">
         <f t="shared" si="4"/>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I18" s="11">
         <f t="shared" si="11"/>
@@ -1585,12 +1585,12 @@
       <c r="K18" s="11"/>
       <c r="L18" s="11">
         <f t="shared" si="8"/>
-        <v>3.3478920000000008</v>
+        <v>3.2652280000000005</v>
       </c>
       <c r="M18" s="11"/>
       <c r="N18" s="11">
         <f t="shared" si="9"/>
-        <v>0.41332000000000013</v>
+        <v>0.45465200000000011</v>
       </c>
       <c r="O18" s="11"/>
     </row>
@@ -1609,19 +1609,19 @@
       </c>
       <c r="E19" s="11">
         <f t="shared" si="10"/>
-        <v>0.51</v>
+        <v>0.45</v>
       </c>
       <c r="F19" s="11">
         <f t="shared" si="2"/>
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="G19" s="11">
         <f t="shared" si="12"/>
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="H19" s="11">
         <f t="shared" si="4"/>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I19" s="11">
         <f t="shared" si="11"/>
@@ -1634,12 +1634,12 @@
       <c r="K19" s="11"/>
       <c r="L19" s="11">
         <f t="shared" si="8"/>
-        <v>2.5648650000000002</v>
+        <v>2.5015350000000005</v>
       </c>
       <c r="M19" s="11"/>
       <c r="N19" s="11">
         <f t="shared" si="9"/>
-        <v>0.31665000000000004</v>
+        <v>0.34831499999999999</v>
       </c>
       <c r="O19" s="11"/>
       <c r="P19" s="17" t="s">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="E20" s="11">
         <f t="shared" si="10"/>
-        <v>0.61</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="F20" s="11">
         <f t="shared" si="2"/>
@@ -1678,11 +1678,11 @@
       </c>
       <c r="G20" s="11">
         <f t="shared" si="12"/>
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="H20" s="11">
         <f t="shared" si="4"/>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I20" s="11">
         <f t="shared" si="11"/>
@@ -1695,22 +1695,22 @@
       <c r="K20" s="11"/>
       <c r="L20" s="11">
         <f t="shared" si="8"/>
-        <v>3.1588380000000003</v>
+        <v>3.0808420000000001</v>
       </c>
       <c r="M20" s="11"/>
       <c r="N20" s="11">
         <f t="shared" si="9"/>
-        <v>0.38997999999999999</v>
+        <v>0.42897800000000003</v>
       </c>
       <c r="O20" s="11"/>
       <c r="P20" s="16" t="s">
         <v>33</v>
       </c>
       <c r="Q20">
-        <v>0.66</v>
+        <v>0.6</v>
       </c>
       <c r="S20">
-        <v>0.04</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="21" spans="1:23">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="E21" s="11">
         <f t="shared" si="10"/>
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="F21" s="11">
         <f t="shared" si="2"/>
@@ -1736,11 +1736,11 @@
       </c>
       <c r="G21" s="11">
         <f t="shared" si="12"/>
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="H21" s="11">
         <f t="shared" si="4"/>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I21" s="11">
         <f t="shared" si="11"/>
@@ -1753,22 +1753,22 @@
       <c r="K21" s="11"/>
       <c r="L21" s="11">
         <f t="shared" si="8"/>
-        <v>4.3198110000000005</v>
+        <v>4.2131490000000005</v>
       </c>
       <c r="M21" s="11"/>
       <c r="N21" s="11">
         <f t="shared" si="9"/>
-        <v>0.53331000000000006</v>
+        <v>0.58664100000000008</v>
       </c>
       <c r="O21" s="11"/>
       <c r="P21" s="16" t="s">
         <v>41</v>
       </c>
       <c r="Q21">
-        <v>0.66</v>
+        <v>0.6</v>
       </c>
       <c r="S21">
-        <v>0.04</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="22" spans="1:23">
@@ -1786,19 +1786,19 @@
       </c>
       <c r="E22" s="11">
         <f t="shared" si="10"/>
-        <v>0.56000000000000005</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="F22" s="11">
         <f t="shared" si="2"/>
-        <v>7.0000000000000007E-2</v>
+        <v>0.13</v>
       </c>
       <c r="G22" s="11">
         <f t="shared" si="12"/>
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="H22" s="11">
         <f t="shared" si="4"/>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I22" s="11">
         <f t="shared" si="11"/>
@@ -1811,21 +1811,21 @@
       <c r="K22" s="11"/>
       <c r="L22" s="11">
         <f t="shared" si="8"/>
-        <v>3.7797840000000007</v>
+        <v>3.6864560000000006</v>
       </c>
       <c r="M22" s="11"/>
       <c r="N22" s="11">
         <f t="shared" si="9"/>
-        <v>0.46664000000000011</v>
+        <v>0.51330400000000009</v>
       </c>
       <c r="P22" s="16" t="s">
         <v>34</v>
       </c>
       <c r="Q22">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="S22">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="23" spans="1:23">
@@ -1843,19 +1843,19 @@
       </c>
       <c r="E23" s="11">
         <f t="shared" si="10"/>
-        <v>0.66</v>
+        <v>0.6</v>
       </c>
       <c r="F23" s="11">
         <f t="shared" si="2"/>
-        <v>0.04</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G23" s="11">
         <f t="shared" si="12"/>
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="H23" s="11">
         <f t="shared" si="4"/>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I23" s="11">
         <f t="shared" si="11"/>
@@ -1868,21 +1868,21 @@
       <c r="K23" s="11"/>
       <c r="L23" s="11">
         <f t="shared" si="8"/>
-        <v>3.54780000000001E-2</v>
+        <v>3.4602000000000105E-2</v>
       </c>
       <c r="M23" s="11"/>
       <c r="N23" s="11">
         <f t="shared" si="9"/>
-        <v>4.3800000000000124E-3</v>
+        <v>4.8180000000000141E-3</v>
       </c>
       <c r="P23" s="16" t="s">
         <v>35</v>
       </c>
       <c r="Q23">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="S23">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="24" spans="1:23">
@@ -1890,10 +1890,10 @@
         <v>36</v>
       </c>
       <c r="Q24">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="S24">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="25" spans="1:23">
@@ -1902,10 +1902,10 @@
         <v>37</v>
       </c>
       <c r="Q25">
-        <v>0.51</v>
+        <v>0.45</v>
       </c>
       <c r="S25">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="26" spans="1:23">
@@ -1914,7 +1914,7 @@
         <v>38</v>
       </c>
       <c r="Q26">
-        <v>0.61</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="S26">
         <v>0.09</v>
@@ -1926,7 +1926,7 @@
         <v>39</v>
       </c>
       <c r="Q27">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="S27">
         <v>0.03</v>
@@ -1938,10 +1938,10 @@
         <v>40</v>
       </c>
       <c r="Q28">
-        <v>0.56000000000000005</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="S28">
-        <v>7.0000000000000007E-2</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="29" spans="1:23">
@@ -1950,10 +1950,10 @@
         <v>9</v>
       </c>
       <c r="Q29">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="S29">
-        <v>7.0000000000000007E-2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="30" spans="1:23">

--- a/packages/calculators/src/modules/test/14-electricity.xlsx
+++ b/packages/calculators/src/modules/test/14-electricity.xlsx
@@ -3,11 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mackcheesman/Desktop/Work/EAP/Code/emissions-calculators/packages/calculators/src/modules/test/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27BA3B66-F57E-3448-BA5C-F3FCD1B335D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="15900" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>

--- a/packages/calculators/src/modules/test/14-electricity.xlsx
+++ b/packages/calculators/src/modules/test/14-electricity.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27BA3B66-F57E-3448-BA5C-F3FCD1B335D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{885DCABE-316C-2047-A8D7-4EC01BCF66F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="15900" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
   </bookViews>
@@ -989,7 +989,7 @@
         <v>14</v>
       </c>
       <c r="Q5">
-        <v>0.79510000000000003</v>
+        <v>0.76129999999999998</v>
       </c>
       <c r="R5" t="s">
         <v>20</v>
@@ -1326,11 +1326,11 @@
       </c>
       <c r="I13" s="11">
         <f t="shared" si="1"/>
-        <v>0.79510000000000003</v>
+        <v>0.76129999999999998</v>
       </c>
       <c r="J13" s="11">
         <f t="shared" si="5"/>
-        <v>343.80000000000013</v>
+        <v>648.00000000000057</v>
       </c>
       <c r="K13" s="11">
         <f t="shared" si="6"/>
@@ -1854,21 +1854,21 @@
       </c>
       <c r="I23" s="11">
         <f t="shared" si="11"/>
-        <v>0.79510000000000003</v>
+        <v>0.76129999999999998</v>
       </c>
       <c r="J23" s="11">
         <f t="shared" si="5"/>
-        <v>43.800000000000125</v>
+        <v>348.00000000000057</v>
       </c>
       <c r="K23" s="11"/>
       <c r="L23" s="11">
         <f t="shared" si="8"/>
-        <v>3.4602000000000105E-2</v>
+        <v>0.2749200000000005</v>
       </c>
       <c r="M23" s="11"/>
       <c r="N23" s="11">
         <f t="shared" si="9"/>
-        <v>4.8180000000000141E-3</v>
+        <v>3.8280000000000064E-2</v>
       </c>
       <c r="P23" s="16" t="s">
         <v>35</v>

--- a/packages/calculators/src/modules/test/14-electricity.xlsx
+++ b/packages/calculators/src/modules/test/14-electricity.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20066D07-B7A9-FD4E-8E1A-6773CAF67D66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{885DCABE-316C-2047-A8D7-4EC01BCF66F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="15900" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
   </bookViews>
@@ -952,19 +952,19 @@
       <c r="D5" s="11"/>
       <c r="E5" s="11">
         <f t="shared" ref="E5:E13" si="0">IF(ISBLANK(A5), "", VLOOKUP(B5, $P$20:$T$28, 2, FALSE))</f>
-        <v>0.66</v>
+        <v>0.6</v>
       </c>
       <c r="F5" s="11">
         <f>IF(ISBLANK(A5), "", VLOOKUP(B5, $P$20:$T$28, 4, FALSE))</f>
-        <v>0.04</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G5" s="11">
         <f>$Q$15</f>
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="H5" s="11">
         <f>$R$15</f>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I5" s="11">
         <f t="shared" ref="I5:I13" si="1">IF(ISBLANK(A5), "", IF(B5="act", $Q$5, 0))</f>
@@ -976,12 +976,12 @@
       </c>
       <c r="K5" s="11">
         <f>A5*E5/1000</f>
-        <v>0.66</v>
+        <v>0.6</v>
       </c>
       <c r="L5" s="11"/>
       <c r="M5" s="11">
         <f>IF(ISBLANK(A5), "", A5*F5/1000)</f>
-        <v>0.04</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="N5" s="11"/>
       <c r="O5" s="11"/>
@@ -989,7 +989,7 @@
         <v>14</v>
       </c>
       <c r="Q5">
-        <v>0.79510000000000003</v>
+        <v>0.76129999999999998</v>
       </c>
       <c r="R5" t="s">
         <v>20</v>
@@ -1005,19 +1005,19 @@
       <c r="D6" s="11"/>
       <c r="E6" s="11">
         <f t="shared" si="0"/>
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="F6" s="11">
         <f t="shared" ref="F6:F23" si="2">IF(ISBLANK(A6), "", VLOOKUP(B6, $P$20:$T$28, 4, FALSE))</f>
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="G6" s="11">
         <f t="shared" ref="G6:G13" si="3">$Q$15</f>
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="H6" s="11">
         <f t="shared" ref="H6:H23" si="4">$R$15</f>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I6" s="11">
         <f t="shared" si="1"/>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="K6" s="11">
         <f t="shared" ref="K6:K13" si="6">A6*E6/1000</f>
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="L6" s="11"/>
       <c r="M6" s="11">
         <f t="shared" ref="M6:M14" si="7">IF(ISBLANK(A6), "", A6*F6/1000)</f>
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="N6" s="11"/>
       <c r="O6" s="11"/>
@@ -1049,19 +1049,19 @@
       <c r="D7" s="11"/>
       <c r="E7" s="11">
         <f t="shared" si="0"/>
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="F7" s="11">
         <f t="shared" si="2"/>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="G7" s="11">
         <f t="shared" si="3"/>
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="H7" s="11">
         <f t="shared" si="4"/>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I7" s="11">
         <f t="shared" si="1"/>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="K7" s="11">
         <f t="shared" si="6"/>
-        <v>2.13</v>
+        <v>1.95</v>
       </c>
       <c r="L7" s="11"/>
       <c r="M7" s="11">
         <f t="shared" si="7"/>
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="N7" s="11"/>
       <c r="O7" s="11"/>
@@ -1093,19 +1093,19 @@
       <c r="D8" s="11"/>
       <c r="E8" s="11">
         <f t="shared" si="0"/>
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="F8" s="11">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="G8" s="11">
         <f t="shared" si="3"/>
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="H8" s="11">
         <f t="shared" si="4"/>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I8" s="11">
         <f t="shared" si="1"/>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="K8" s="11">
         <f t="shared" si="6"/>
-        <v>0.92</v>
+        <v>0.84</v>
       </c>
       <c r="L8" s="11"/>
       <c r="M8" s="11">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="N8" s="11"/>
       <c r="O8" s="11"/>
@@ -1137,19 +1137,19 @@
       <c r="D9" s="11"/>
       <c r="E9" s="11">
         <f t="shared" si="0"/>
-        <v>0.51</v>
+        <v>0.45</v>
       </c>
       <c r="F9" s="11">
         <f t="shared" si="2"/>
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="G9" s="11">
         <f t="shared" si="3"/>
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="H9" s="11">
         <f t="shared" si="4"/>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I9" s="11">
         <f t="shared" si="1"/>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="K9" s="11">
         <f t="shared" si="6"/>
-        <v>2.5499999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="L9" s="11"/>
       <c r="M9" s="11">
         <f t="shared" si="7"/>
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="N9" s="11"/>
     </row>
@@ -1180,7 +1180,7 @@
       <c r="D10" s="11"/>
       <c r="E10" s="11">
         <f t="shared" si="0"/>
-        <v>0.61</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="F10" s="11">
         <f t="shared" si="2"/>
@@ -1188,11 +1188,11 @@
       </c>
       <c r="G10" s="11">
         <f t="shared" si="3"/>
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="H10" s="11">
         <f t="shared" si="4"/>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I10" s="11">
         <f t="shared" si="1"/>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="K10" s="11">
         <f t="shared" si="6"/>
-        <v>3.66</v>
+        <v>3.3600000000000003</v>
       </c>
       <c r="L10" s="11"/>
       <c r="M10" s="11">
@@ -1223,7 +1223,7 @@
       <c r="D11" s="11"/>
       <c r="E11" s="11">
         <f t="shared" si="0"/>
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="F11" s="11">
         <f t="shared" si="2"/>
@@ -1231,11 +1231,11 @@
       </c>
       <c r="G11" s="11">
         <f t="shared" si="3"/>
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="H11" s="11">
         <f t="shared" si="4"/>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I11" s="11">
         <f t="shared" si="1"/>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="K11" s="11">
         <f t="shared" si="6"/>
-        <v>1.05</v>
+        <v>1.47</v>
       </c>
       <c r="L11" s="11"/>
       <c r="M11" s="11">
@@ -1266,19 +1266,19 @@
       <c r="D12" s="11"/>
       <c r="E12" s="11">
         <f t="shared" si="0"/>
-        <v>0.56000000000000005</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="F12" s="11">
         <f t="shared" si="2"/>
-        <v>7.0000000000000007E-2</v>
+        <v>0.13</v>
       </c>
       <c r="G12" s="11">
         <f t="shared" si="3"/>
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="H12" s="11">
         <f t="shared" si="4"/>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I12" s="11">
         <f t="shared" si="1"/>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="K12" s="11">
         <f t="shared" si="6"/>
-        <v>4.4800000000000004</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L12" s="11"/>
       <c r="M12" s="11">
         <f t="shared" si="7"/>
-        <v>0.56000000000000005</v>
+        <v>1.04</v>
       </c>
       <c r="N12" s="11"/>
     </row>
@@ -1310,36 +1310,36 @@
       <c r="D13" s="11"/>
       <c r="E13" s="11">
         <f t="shared" si="0"/>
-        <v>0.66</v>
+        <v>0.6</v>
       </c>
       <c r="F13" s="11">
         <f t="shared" si="2"/>
-        <v>0.04</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G13" s="11">
         <f t="shared" si="3"/>
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="H13" s="11">
         <f t="shared" si="4"/>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I13" s="11">
         <f t="shared" si="1"/>
-        <v>0.79510000000000003</v>
+        <v>0.76129999999999998</v>
       </c>
       <c r="J13" s="11">
         <f t="shared" si="5"/>
-        <v>343.80000000000013</v>
+        <v>648.00000000000057</v>
       </c>
       <c r="K13" s="11">
         <f t="shared" si="6"/>
-        <v>5.94</v>
+        <v>5.4</v>
       </c>
       <c r="L13" s="11"/>
       <c r="M13" s="11">
         <f t="shared" si="7"/>
-        <v>0.36</v>
+        <v>0.63000000000000012</v>
       </c>
       <c r="N13" s="11"/>
       <c r="O13" s="11"/>
@@ -1399,19 +1399,19 @@
       </c>
       <c r="E15" s="11">
         <f t="shared" ref="E15:E23" si="10">IF(ISBLANK(A15), "", VLOOKUP(B15, $P$20:$T$28, 2, FALSE))</f>
-        <v>0.66</v>
+        <v>0.6</v>
       </c>
       <c r="F15" s="11">
         <f t="shared" si="2"/>
-        <v>0.04</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G15" s="11">
         <f>$Q$15</f>
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="H15" s="11">
         <f t="shared" si="4"/>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I15" s="11">
         <f t="shared" ref="I15:I23" si="11">IF(ISBLANK(A15), "", IF(B15="act", $Q$5, 0))</f>
@@ -1424,22 +1424,22 @@
       <c r="K15" s="11"/>
       <c r="L15" s="11">
         <f>IF(ISBLANK(A15), "", J15*G15/1000)</f>
-        <v>0.43197300000000005</v>
+        <v>0.4213070000000001</v>
       </c>
       <c r="M15" s="11"/>
       <c r="N15" s="11">
         <f t="shared" si="9"/>
-        <v>5.3330000000000009E-2</v>
+        <v>5.8663000000000014E-2</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" t="s">
         <v>9</v>
       </c>
       <c r="Q15">
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="R15">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -1457,19 +1457,19 @@
       </c>
       <c r="E16" s="11">
         <f t="shared" si="10"/>
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="F16" s="11">
         <f t="shared" si="2"/>
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="G16" s="11">
         <f t="shared" ref="G16:G23" si="12">$Q$15</f>
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="H16" s="11">
         <f t="shared" si="4"/>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I16" s="11">
         <f t="shared" si="11"/>
@@ -1482,12 +1482,12 @@
       <c r="K16" s="11"/>
       <c r="L16" s="11">
         <f t="shared" si="8"/>
-        <v>2.5378920000000003</v>
+        <v>2.4752280000000004</v>
       </c>
       <c r="M16" s="11"/>
       <c r="N16" s="11">
         <f t="shared" si="9"/>
-        <v>0.31332000000000004</v>
+        <v>0.34465200000000007</v>
       </c>
       <c r="O16" s="11"/>
     </row>
@@ -1506,19 +1506,19 @@
       </c>
       <c r="E17" s="11">
         <f t="shared" si="10"/>
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="F17" s="11">
         <f t="shared" si="2"/>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="G17" s="11">
         <f t="shared" si="12"/>
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="H17" s="11">
         <f t="shared" si="4"/>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I17" s="11">
         <f t="shared" si="11"/>
@@ -1531,12 +1531,12 @@
       <c r="K17" s="11"/>
       <c r="L17" s="11">
         <f t="shared" si="8"/>
-        <v>1.862919</v>
+        <v>1.816921</v>
       </c>
       <c r="M17" s="11"/>
       <c r="N17" s="11">
         <f t="shared" si="9"/>
-        <v>0.22999</v>
+        <v>0.25298900000000002</v>
       </c>
       <c r="O17" s="11"/>
     </row>
@@ -1555,19 +1555,19 @@
       </c>
       <c r="E18" s="11">
         <f t="shared" si="10"/>
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="F18" s="11">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="G18" s="11">
         <f t="shared" si="12"/>
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="H18" s="11">
         <f t="shared" si="4"/>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I18" s="11">
         <f t="shared" si="11"/>
@@ -1580,12 +1580,12 @@
       <c r="K18" s="11"/>
       <c r="L18" s="11">
         <f t="shared" si="8"/>
-        <v>3.3478920000000008</v>
+        <v>3.2652280000000005</v>
       </c>
       <c r="M18" s="11"/>
       <c r="N18" s="11">
         <f t="shared" si="9"/>
-        <v>0.41332000000000013</v>
+        <v>0.45465200000000011</v>
       </c>
       <c r="O18" s="11"/>
     </row>
@@ -1604,19 +1604,19 @@
       </c>
       <c r="E19" s="11">
         <f t="shared" si="10"/>
-        <v>0.51</v>
+        <v>0.45</v>
       </c>
       <c r="F19" s="11">
         <f t="shared" si="2"/>
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="G19" s="11">
         <f t="shared" si="12"/>
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="H19" s="11">
         <f t="shared" si="4"/>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I19" s="11">
         <f t="shared" si="11"/>
@@ -1629,12 +1629,12 @@
       <c r="K19" s="11"/>
       <c r="L19" s="11">
         <f t="shared" si="8"/>
-        <v>2.5648650000000002</v>
+        <v>2.5015350000000005</v>
       </c>
       <c r="M19" s="11"/>
       <c r="N19" s="11">
         <f t="shared" si="9"/>
-        <v>0.31665000000000004</v>
+        <v>0.34831499999999999</v>
       </c>
       <c r="O19" s="11"/>
       <c r="P19" s="17" t="s">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="E20" s="11">
         <f t="shared" si="10"/>
-        <v>0.61</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="F20" s="11">
         <f t="shared" si="2"/>
@@ -1673,11 +1673,11 @@
       </c>
       <c r="G20" s="11">
         <f t="shared" si="12"/>
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="H20" s="11">
         <f t="shared" si="4"/>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I20" s="11">
         <f t="shared" si="11"/>
@@ -1690,22 +1690,22 @@
       <c r="K20" s="11"/>
       <c r="L20" s="11">
         <f t="shared" si="8"/>
-        <v>3.1588380000000003</v>
+        <v>3.0808420000000001</v>
       </c>
       <c r="M20" s="11"/>
       <c r="N20" s="11">
         <f t="shared" si="9"/>
-        <v>0.38997999999999999</v>
+        <v>0.42897800000000003</v>
       </c>
       <c r="O20" s="11"/>
       <c r="P20" s="16" t="s">
         <v>33</v>
       </c>
       <c r="Q20">
-        <v>0.66</v>
+        <v>0.6</v>
       </c>
       <c r="S20">
-        <v>0.04</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="21" spans="1:23">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="E21" s="11">
         <f t="shared" si="10"/>
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="F21" s="11">
         <f t="shared" si="2"/>
@@ -1731,11 +1731,11 @@
       </c>
       <c r="G21" s="11">
         <f t="shared" si="12"/>
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="H21" s="11">
         <f t="shared" si="4"/>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I21" s="11">
         <f t="shared" si="11"/>
@@ -1748,22 +1748,22 @@
       <c r="K21" s="11"/>
       <c r="L21" s="11">
         <f t="shared" si="8"/>
-        <v>4.3198110000000005</v>
+        <v>4.2131490000000005</v>
       </c>
       <c r="M21" s="11"/>
       <c r="N21" s="11">
         <f t="shared" si="9"/>
-        <v>0.53331000000000006</v>
+        <v>0.58664100000000008</v>
       </c>
       <c r="O21" s="11"/>
       <c r="P21" s="16" t="s">
         <v>41</v>
       </c>
       <c r="Q21">
-        <v>0.66</v>
+        <v>0.6</v>
       </c>
       <c r="S21">
-        <v>0.04</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="22" spans="1:23">
@@ -1781,19 +1781,19 @@
       </c>
       <c r="E22" s="11">
         <f t="shared" si="10"/>
-        <v>0.56000000000000005</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="F22" s="11">
         <f t="shared" si="2"/>
-        <v>7.0000000000000007E-2</v>
+        <v>0.13</v>
       </c>
       <c r="G22" s="11">
         <f t="shared" si="12"/>
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="H22" s="11">
         <f t="shared" si="4"/>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I22" s="11">
         <f t="shared" si="11"/>
@@ -1806,21 +1806,21 @@
       <c r="K22" s="11"/>
       <c r="L22" s="11">
         <f t="shared" si="8"/>
-        <v>3.7797840000000007</v>
+        <v>3.6864560000000006</v>
       </c>
       <c r="M22" s="11"/>
       <c r="N22" s="11">
         <f t="shared" si="9"/>
-        <v>0.46664000000000011</v>
+        <v>0.51330400000000009</v>
       </c>
       <c r="P22" s="16" t="s">
         <v>34</v>
       </c>
       <c r="Q22">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="S22">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="23" spans="1:23">
@@ -1838,46 +1838,46 @@
       </c>
       <c r="E23" s="11">
         <f t="shared" si="10"/>
-        <v>0.66</v>
+        <v>0.6</v>
       </c>
       <c r="F23" s="11">
         <f t="shared" si="2"/>
-        <v>0.04</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G23" s="11">
         <f t="shared" si="12"/>
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="H23" s="11">
         <f t="shared" si="4"/>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I23" s="11">
         <f t="shared" si="11"/>
-        <v>0.79510000000000003</v>
+        <v>0.76129999999999998</v>
       </c>
       <c r="J23" s="11">
         <f t="shared" si="5"/>
-        <v>43.800000000000125</v>
+        <v>348.00000000000057</v>
       </c>
       <c r="K23" s="11"/>
       <c r="L23" s="11">
         <f t="shared" si="8"/>
-        <v>3.54780000000001E-2</v>
+        <v>0.2749200000000005</v>
       </c>
       <c r="M23" s="11"/>
       <c r="N23" s="11">
         <f t="shared" si="9"/>
-        <v>4.3800000000000124E-3</v>
+        <v>3.8280000000000064E-2</v>
       </c>
       <c r="P23" s="16" t="s">
         <v>35</v>
       </c>
       <c r="Q23">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="S23">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="24" spans="1:23">
@@ -1885,10 +1885,10 @@
         <v>36</v>
       </c>
       <c r="Q24">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="S24">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="25" spans="1:23">
@@ -1897,10 +1897,10 @@
         <v>37</v>
       </c>
       <c r="Q25">
-        <v>0.51</v>
+        <v>0.45</v>
       </c>
       <c r="S25">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="26" spans="1:23">
@@ -1909,7 +1909,7 @@
         <v>38</v>
       </c>
       <c r="Q26">
-        <v>0.61</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="S26">
         <v>0.09</v>
@@ -1921,7 +1921,7 @@
         <v>39</v>
       </c>
       <c r="Q27">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="S27">
         <v>0.03</v>
@@ -1933,10 +1933,10 @@
         <v>40</v>
       </c>
       <c r="Q28">
-        <v>0.56000000000000005</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="S28">
-        <v>7.0000000000000007E-2</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="29" spans="1:23">
@@ -1945,10 +1945,10 @@
         <v>9</v>
       </c>
       <c r="Q29">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="S29">
-        <v>7.0000000000000007E-2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="30" spans="1:23">
